--- a/example-data/dummydata-a2.xlsx
+++ b/example-data/dummydata-a2.xlsx
@@ -409,1015 +409,1015 @@
     <t>a2_auteursrechtHouder_1</t>
   </si>
   <si>
-    <t>2029-02-17</t>
+    <t>2028-02-26</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_2</t>
+  </si>
+  <si>
+    <t>a2_producent_1</t>
+  </si>
+  <si>
+    <t>2007-10-03T01:45:59.468Z</t>
+  </si>
+  <si>
+    <t>a2_taal_1</t>
+  </si>
+  <si>
+    <t>a2_uitgever_1</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_1</t>
+  </si>
+  <si>
+    <t>a2_versie_1</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_2</t>
+  </si>
+  <si>
+    <t>a2_auteur_2</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_2</t>
+  </si>
+  <si>
+    <t>2029-05-21</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_4</t>
+  </si>
+  <si>
+    <t>a2_producent_2</t>
+  </si>
+  <si>
+    <t>2002-12-28T20:00:37.958Z</t>
+  </si>
+  <si>
+    <t>a2_taal_2</t>
+  </si>
+  <si>
+    <t>a2_uitgever_2</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_2</t>
+  </si>
+  <si>
+    <t>a2_versie_2</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_3</t>
+  </si>
+  <si>
+    <t>a2_auteur_3</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_3</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_1</t>
+  </si>
+  <si>
+    <t>a2_producent_3</t>
+  </si>
+  <si>
+    <t>2009-07-13T22:58:43.915Z</t>
+  </si>
+  <si>
+    <t>a2_taal_3</t>
+  </si>
+  <si>
+    <t>a2_uitgever_3</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_3</t>
+  </si>
+  <si>
+    <t>a2_versie_3</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_4</t>
+  </si>
+  <si>
+    <t>a2_auteur_4</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_4</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>a2_producent_4</t>
+  </si>
+  <si>
+    <t>2012-12-31T21:21:00.473Z</t>
+  </si>
+  <si>
+    <t>a2_taal_4</t>
+  </si>
+  <si>
+    <t>a2_uitgever_4</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_4</t>
+  </si>
+  <si>
+    <t>a2_versie_4</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_5</t>
+  </si>
+  <si>
+    <t>a2_auteur_5|a2_auteur_5b</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
+  </si>
+  <si>
+    <t>2019-06-18</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_3|a2/code/Licentie_1</t>
+  </si>
+  <si>
+    <t>a2_producent_5|a2_producent_5b</t>
+  </si>
+  <si>
+    <t>2030-08-24T04:52:17.103Z</t>
+  </si>
+  <si>
+    <t>a2_taal_5|a2_taal_5b</t>
+  </si>
+  <si>
+    <t>a2_uitgever_5|a2_uitgever_5b</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_5</t>
+  </si>
+  <si>
+    <t>a2_versie_5</t>
+  </si>
+  <si>
+    <t>bestaatUit</t>
+  </si>
+  <si>
+    <t>bron</t>
+  </si>
+  <si>
+    <t>competentie</t>
+  </si>
+  <si>
+    <t>doelgroep</t>
+  </si>
+  <si>
+    <t>gedefinieerdDoor</t>
+  </si>
+  <si>
+    <t>geldigheid</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>gerelateerdAan</t>
+  </si>
+  <si>
+    <t>heeftSpecialisatie</t>
+  </si>
+  <si>
+    <t>identificator</t>
+  </si>
+  <si>
+    <t>isBrederDan</t>
+  </si>
+  <si>
+    <t>isLidVan</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>onderwerp</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2_bron_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_1</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_1</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_1</t>
+  </si>
+  <si>
+    <t>a2_bron_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_2</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_2</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_2</t>
+  </si>
+  <si>
+    <t>a2_bron_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_3</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_5</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3</t>
+  </si>
+  <si>
+    <t>a2_niveau_3</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_3</t>
+  </si>
+  <si>
+    <t>a2_bron_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_5</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_4</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_4</t>
+  </si>
+  <si>
+    <t>a2_niveau_4</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2_bron_5|a2_bron_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_1|a2/code/Competentie_2</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_2|a2/code/DoelCollectie_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_5|a2_niveau_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
+  </si>
+  <si>
+    <t>a2_type_5|a2_type_5b</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_5</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_5</t>
+  </si>
+  <si>
+    <t>leeftijdstype</t>
+  </si>
+  <si>
+    <t>onderwijsniveau</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_1</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_1</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_2</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_2</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_3</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_4</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_4</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
+  </si>
+  <si>
+    <t>valuta</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_1</t>
+  </si>
+  <si>
+    <t>a2_valuta_1</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_2</t>
+  </si>
+  <si>
+    <t>a2_valuta_2</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_3</t>
+  </si>
+  <si>
+    <t>a2_valuta_3</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_4</t>
+  </si>
+  <si>
+    <t>a2_valuta_4</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_5</t>
+  </si>
+  <si>
+    <t>a2_valuta_5</t>
+  </si>
+  <si>
+    <t>toegekendDoor</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_1</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_4</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_5</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
+    <t>waarde</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_1</t>
+  </si>
+  <si>
+    <t>a2_eenheid_1</t>
+  </si>
+  <si>
+    <t>a2_waarde_1</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_2</t>
+  </si>
+  <si>
+    <t>a2_eenheid_2</t>
+  </si>
+  <si>
+    <t>a2_waarde_2</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_3</t>
+  </si>
+  <si>
+    <t>a2_eenheid_3</t>
+  </si>
+  <si>
+    <t>a2_waarde_3</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_4</t>
+  </si>
+  <si>
+    <t>a2_eenheid_4</t>
+  </si>
+  <si>
+    <t>a2_waarde_4</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_5</t>
+  </si>
+  <si>
+    <t>a2_eenheid_5</t>
+  </si>
+  <si>
+    <t>a2_waarde_5</t>
+  </si>
+  <si>
+    <t>draagtBijAanHetBehalenVan</t>
+  </si>
+  <si>
+    <t>heeftDeel</t>
+  </si>
+  <si>
+    <t>ingerichtDoor</t>
+  </si>
+  <si>
+    <t>isDeelVan</t>
+  </si>
+  <si>
+    <t>leermiddel</t>
+  </si>
+  <si>
+    <t>locatie</t>
+  </si>
+  <si>
+    <t>periode</t>
+  </si>
+  <si>
+    <t>specificatie</t>
+  </si>
+  <si>
+    <t>werklast</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2_periode_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_werklast_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2_periode_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4</t>
+  </si>
+  <si>
+    <t>a2_periode_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_4</t>
+  </si>
+  <si>
+    <t>a2_periode_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2_werklast_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5|a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1|a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Adresvoorstelling_5|a2/code/Adresvoorstelling_5</t>
+  </si>
+  <si>
+    <t>a2_periode_5|a2_periode_5b</t>
+  </si>
+  <si>
+    <t>a2_werklast_5</t>
+  </si>
+  <si>
+    <t>contacturen</t>
+  </si>
+  <si>
+    <t>generalisatieVan</t>
+  </si>
+  <si>
+    <t>instructietaal</t>
+  </si>
+  <si>
+    <t>schrijftVoor</t>
+  </si>
+  <si>
+    <t>specialisatieVan</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_3</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_5|a2/code/Openingsurenspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4|a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>benodigdMateriaal</t>
+  </si>
+  <si>
+    <t>dient</t>
+  </si>
+  <si>
+    <t>formaat</t>
+  </si>
+  <si>
+    <t>instructie</t>
+  </si>
+  <si>
+    <t>interactieType</t>
+  </si>
+  <si>
+    <t>kost</t>
+  </si>
+  <si>
+    <t>resultaat</t>
+  </si>
+  <si>
+    <t>sleutelwoord</t>
+  </si>
+  <si>
+    <t>toegankelijkheid</t>
+  </si>
+  <si>
+    <t>vereiste</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_5</t>
+  </si>
+  <si>
+    <t>a2_formaat_1</t>
+  </si>
+  <si>
+    <t>a2_instructie_1</t>
+  </si>
+  <si>
+    <t>a2_interactieType_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_5</t>
+  </si>
+  <si>
+    <t>a2_resultaat_1</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_1</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_1</t>
+  </si>
+  <si>
+    <t>a2_vereiste_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2_formaat_2</t>
+  </si>
+  <si>
+    <t>a2_instructie_2</t>
+  </si>
+  <si>
+    <t>a2_interactieType_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2_resultaat_2</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_2</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_2</t>
+  </si>
+  <si>
+    <t>a2_vereiste_2</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_3</t>
+  </si>
+  <si>
+    <t>a2_formaat_3</t>
+  </si>
+  <si>
+    <t>a2_instructie_3</t>
+  </si>
+  <si>
+    <t>a2_interactieType_3</t>
+  </si>
+  <si>
+    <t>a2_resultaat_3</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_3</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_3</t>
+  </si>
+  <si>
+    <t>a2_vereiste_3</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_3</t>
+  </si>
+  <si>
+    <t>a2_formaat_4</t>
+  </si>
+  <si>
+    <t>a2_instructie_4</t>
+  </si>
+  <si>
+    <t>a2_interactieType_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_4</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_4</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_4</t>
+  </si>
+  <si>
+    <t>a2_vereiste_4</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2|a2/code/LeermiddelElement_5</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_3|a2/code/Competentie_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2_formaat_5|a2_formaat_5b</t>
+  </si>
+  <si>
+    <t>a2_instructie_5</t>
+  </si>
+  <si>
+    <t>a2_interactieType_5|a2_interactieType_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3|a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2_resultaat_5|a2_resultaat_5b</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_5</t>
+  </si>
+  <si>
+    <t>a2_vereiste_5|a2_vereiste_5b</t>
+  </si>
+  <si>
+    <t>onderdeelVan</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_3</t>
   </si>
   <si>
     <t>a2/code/Licentie_5</t>
   </si>
   <si>
-    <t>a2_producent_1</t>
-  </si>
-  <si>
-    <t>2012-04-29T13:28:45.990Z</t>
-  </si>
-  <si>
-    <t>a2_taal_1</t>
-  </si>
-  <si>
-    <t>a2_uitgever_1</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_1</t>
-  </si>
-  <si>
-    <t>a2_versie_1</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_2</t>
-  </si>
-  <si>
-    <t>a2_auteur_2</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_2</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_3</t>
-  </si>
-  <si>
-    <t>a2_producent_2</t>
-  </si>
-  <si>
-    <t>2014-07-31T02:36:46.143Z</t>
-  </si>
-  <si>
-    <t>a2_taal_2</t>
-  </si>
-  <si>
-    <t>a2_uitgever_2</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_2</t>
-  </si>
-  <si>
-    <t>a2_versie_2</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_3</t>
-  </si>
-  <si>
-    <t>a2_auteur_3</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_3</t>
-  </si>
-  <si>
-    <t>2018-06-01</t>
-  </si>
-  <si>
-    <t>a2_producent_3</t>
-  </si>
-  <si>
-    <t>2007-11-06T18:37:21.280Z</t>
-  </si>
-  <si>
-    <t>a2_taal_3</t>
-  </si>
-  <si>
-    <t>a2_uitgever_3</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_3</t>
-  </si>
-  <si>
-    <t>a2_versie_3</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_4</t>
-  </si>
-  <si>
-    <t>a2_auteur_4</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_4</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2_producent_4</t>
-  </si>
-  <si>
-    <t>2017-07-14T17:55:41.401Z</t>
-  </si>
-  <si>
-    <t>a2_taal_4</t>
-  </si>
-  <si>
-    <t>a2_uitgever_4</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_4</t>
-  </si>
-  <si>
-    <t>a2_versie_4</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_5</t>
-  </si>
-  <si>
-    <t>a2_auteur_5|a2_auteur_5b</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
-  </si>
-  <si>
-    <t>2016-09-10</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_4|a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2_producent_5|a2_producent_5b</t>
-  </si>
-  <si>
-    <t>2023-06-17T20:20:28.239Z</t>
-  </si>
-  <si>
-    <t>a2_taal_5|a2_taal_5b</t>
-  </si>
-  <si>
-    <t>a2_uitgever_5|a2_uitgever_5b</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_5</t>
-  </si>
-  <si>
-    <t>a2_versie_5</t>
-  </si>
-  <si>
-    <t>bestaatUit</t>
-  </si>
-  <si>
-    <t>bron</t>
-  </si>
-  <si>
-    <t>competentie</t>
-  </si>
-  <si>
-    <t>doelgroep</t>
-  </si>
-  <si>
-    <t>gedefinieerdDoor</t>
-  </si>
-  <si>
-    <t>geldigheid</t>
-  </si>
-  <si>
-    <t>gelijkaardig</t>
-  </si>
-  <si>
-    <t>gerelateerdAan</t>
-  </si>
-  <si>
-    <t>heeftSpecialisatie</t>
-  </si>
-  <si>
-    <t>identificator</t>
-  </si>
-  <si>
-    <t>isBrederDan</t>
-  </si>
-  <si>
-    <t>isLidVan</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>onderwerp</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_bron_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_1</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_5</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_3</t>
-  </si>
-  <si>
-    <t>a2_niveau_1</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_1</t>
-  </si>
-  <si>
-    <t>a2_bron_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_2</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_niveau_2</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2_bron_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_5</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_3</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_3</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_3</t>
-  </si>
-  <si>
-    <t>a2_bron_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_4</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_4</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_3</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_4</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_bron_5|a2_bron_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_3|a2/code/Competentie_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_5|a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_5|a2_niveau_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
-  </si>
-  <si>
-    <t>a2_type_5|a2_type_5b</t>
-  </si>
-  <si>
-    <t>heeftLid</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_2</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_5</t>
-  </si>
-  <si>
-    <t>leeftijdstype</t>
-  </si>
-  <si>
-    <t>onderwijsniveau</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_1</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_1</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_2</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_3</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_4</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_4</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
-  </si>
-  <si>
-    <t>valuta</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_1</t>
-  </si>
-  <si>
-    <t>a2_valuta_1</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_2</t>
-  </si>
-  <si>
-    <t>a2_valuta_2</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_3</t>
-  </si>
-  <si>
-    <t>a2_valuta_3</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_4</t>
-  </si>
-  <si>
-    <t>a2_valuta_4</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_5</t>
-  </si>
-  <si>
-    <t>a2_valuta_5</t>
-  </si>
-  <si>
-    <t>toegekendDoor</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_1</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_2</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_5</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
-    <t>waarde</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_1</t>
-  </si>
-  <si>
-    <t>a2_eenheid_1</t>
-  </si>
-  <si>
-    <t>a2_waarde_1</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_2</t>
-  </si>
-  <si>
-    <t>a2_eenheid_2</t>
-  </si>
-  <si>
-    <t>a2_waarde_2</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_3</t>
-  </si>
-  <si>
-    <t>a2_eenheid_3</t>
-  </si>
-  <si>
-    <t>a2_waarde_3</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_4</t>
-  </si>
-  <si>
-    <t>a2_eenheid_4</t>
-  </si>
-  <si>
-    <t>a2_waarde_4</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_5</t>
-  </si>
-  <si>
-    <t>a2_eenheid_5</t>
-  </si>
-  <si>
-    <t>a2_waarde_5</t>
-  </si>
-  <si>
-    <t>draagtBijAanHetBehalenVan</t>
-  </si>
-  <si>
-    <t>heeftDeel</t>
-  </si>
-  <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
-    <t>isDeelVan</t>
-  </si>
-  <si>
-    <t>leermiddel</t>
-  </si>
-  <si>
-    <t>locatie</t>
-  </si>
-  <si>
-    <t>periode</t>
-  </si>
-  <si>
-    <t>specificatie</t>
-  </si>
-  <si>
-    <t>werklast</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2_periode_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_2</t>
-  </si>
-  <si>
-    <t>a2_periode_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_werklast_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2_periode_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_4</t>
-  </si>
-  <si>
-    <t>a2_periode_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_werklast_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4|a2/code/Leeractiviteit_1</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5|a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1|a2/code/Leermiddel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Adresvoorstelling_5|a2/code/Adresvoorstelling_5</t>
-  </si>
-  <si>
-    <t>a2_periode_5|a2_periode_5b</t>
-  </si>
-  <si>
-    <t>a2_werklast_5</t>
-  </si>
-  <si>
-    <t>contacturen</t>
-  </si>
-  <si>
-    <t>generalisatieVan</t>
-  </si>
-  <si>
-    <t>instructietaal</t>
-  </si>
-  <si>
-    <t>schrijftVoor</t>
-  </si>
-  <si>
-    <t>specialisatieVan</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_2</t>
+    <t>dagVanDeWeek</t>
+  </si>
+  <si>
+    <t>geldigTot</t>
+  </si>
+  <si>
+    <t>geldigVan</t>
+  </si>
+  <si>
+    <t>gesloten</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_1</t>
+  </si>
+  <si>
+    <t>2002-10-22T00:56:42.762Z</t>
+  </si>
+  <si>
+    <t>2029-01-29T06:29:01.072Z</t>
+  </si>
+  <si>
+    <t>11:40:50</t>
+  </si>
+  <si>
+    <t>07:03:14</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_2</t>
+  </si>
+  <si>
+    <t>2024-07-18T21:35:49.315Z</t>
+  </si>
+  <si>
+    <t>2016-08-21T14:05:54.029Z</t>
+  </si>
+  <si>
+    <t>14:51:59</t>
+  </si>
+  <si>
+    <t>08:56:04</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_3</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_3</t>
+  </si>
+  <si>
+    <t>2025-04-24T09:32:43.191Z</t>
+  </si>
+  <si>
+    <t>2001-01-13T16:41:53.054Z</t>
+  </si>
+  <si>
+    <t>17:27:03</t>
+  </si>
+  <si>
+    <t>13:49:49</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_4</t>
   </si>
   <si>
-    <t>a2_instructietaal_3</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_3|a2/code/Openingsurenspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1|a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>benodigdMateriaal</t>
-  </si>
-  <si>
-    <t>dient</t>
-  </si>
-  <si>
-    <t>formaat</t>
-  </si>
-  <si>
-    <t>instructie</t>
-  </si>
-  <si>
-    <t>interactieType</t>
-  </si>
-  <si>
-    <t>kost</t>
-  </si>
-  <si>
-    <t>resultaat</t>
-  </si>
-  <si>
-    <t>sleutelwoord</t>
-  </si>
-  <si>
-    <t>toegankelijkheid</t>
-  </si>
-  <si>
-    <t>vereiste</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_5</t>
-  </si>
-  <si>
-    <t>a2_formaat_1</t>
-  </si>
-  <si>
-    <t>a2_instructie_1</t>
-  </si>
-  <si>
-    <t>a2_interactieType_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_5</t>
-  </si>
-  <si>
-    <t>a2_resultaat_1</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_1</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_1</t>
-  </si>
-  <si>
-    <t>a2_vereiste_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2_formaat_2</t>
-  </si>
-  <si>
-    <t>a2_instructie_2</t>
-  </si>
-  <si>
-    <t>a2_interactieType_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_2</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_2</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_2</t>
-  </si>
-  <si>
-    <t>a2_vereiste_2</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_3</t>
-  </si>
-  <si>
-    <t>a2_formaat_3</t>
-  </si>
-  <si>
-    <t>a2_instructie_3</t>
-  </si>
-  <si>
-    <t>a2_interactieType_3</t>
-  </si>
-  <si>
-    <t>a2_resultaat_3</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_3</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_3</t>
-  </si>
-  <si>
-    <t>a2_vereiste_3</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_1</t>
-  </si>
-  <si>
-    <t>a2_formaat_4</t>
-  </si>
-  <si>
-    <t>a2_instructie_4</t>
-  </si>
-  <si>
-    <t>a2_interactieType_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_4</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_4</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_4</t>
-  </si>
-  <si>
-    <t>a2_vereiste_4</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_3|a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_2|a2/code/Competentie_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_formaat_5|a2_formaat_5b</t>
-  </si>
-  <si>
-    <t>a2_instructie_5</t>
-  </si>
-  <si>
-    <t>a2_interactieType_5|a2_interactieType_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4|a2/code/LeermiddelVerzameling_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_5|a2_resultaat_5b</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_5</t>
-  </si>
-  <si>
-    <t>a2_vereiste_5|a2_vereiste_5b</t>
-  </si>
-  <si>
-    <t>onderdeelVan</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_3</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5|a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_2</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_4</t>
-  </si>
-  <si>
-    <t>dagVanDeWeek</t>
-  </si>
-  <si>
-    <t>geldigTot</t>
-  </si>
-  <si>
-    <t>geldigVan</t>
-  </si>
-  <si>
-    <t>gesloten</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_1</t>
-  </si>
-  <si>
-    <t>2012-09-22T08:37:08.467Z</t>
-  </si>
-  <si>
-    <t>2028-12-10T16:07:20.431Z</t>
-  </si>
-  <si>
-    <t>18:06:17</t>
-  </si>
-  <si>
-    <t>12:02:05</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_2</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_2</t>
-  </si>
-  <si>
-    <t>2023-04-11T20:22:46.558Z</t>
-  </si>
-  <si>
-    <t>2012-03-06T10:48:37.078Z</t>
-  </si>
-  <si>
-    <t>13:02:07</t>
-  </si>
-  <si>
-    <t>14:24:42</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_3</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_3</t>
-  </si>
-  <si>
-    <t>2004-02-24T22:52:54.593Z</t>
-  </si>
-  <si>
-    <t>2003-06-23T17:14:15.115Z</t>
-  </si>
-  <si>
-    <t>15:48:08</t>
-  </si>
-  <si>
-    <t>14:53:30</t>
-  </si>
-  <si>
     <t>http://example.com/au/dagVanDeWeek_4</t>
   </si>
   <si>
-    <t>2014-07-07T21:47:10.726Z</t>
-  </si>
-  <si>
-    <t>2002-05-23T20:49:19.272Z</t>
-  </si>
-  <si>
-    <t>23:17:04</t>
-  </si>
-  <si>
-    <t>03:56:17</t>
+    <t>2016-04-05T02:38:48.513Z</t>
+  </si>
+  <si>
+    <t>2024-08-23T02:57:00.428Z</t>
+  </si>
+  <si>
+    <t>03:40:25</t>
+  </si>
+  <si>
+    <t>19:20:40</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_5</t>
   </si>
   <si>
-    <t>2001-10-08T02:42:58.530Z</t>
-  </si>
-  <si>
-    <t>2001-08-14T00:53:52.851Z</t>
-  </si>
-  <si>
-    <t>20:48:08</t>
-  </si>
-  <si>
-    <t>14:48:50</t>
+    <t>2022-08-21T19:22:45.077Z</t>
+  </si>
+  <si>
+    <t>2027-07-28T15:26:21.240Z</t>
+  </si>
+  <si>
+    <t>19:08:04</t>
+  </si>
+  <si>
+    <t>05:49:49</t>
   </si>
   <si>
     <t>tot</t>
@@ -2316,7 +2316,7 @@
         <v>312</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>313</v>
@@ -2336,45 +2336,45 @@
         <v>316</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>317</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>322</v>
@@ -2386,13 +2386,13 @@
         <v>323</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>324</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
@@ -2403,72 +2403,72 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -2490,28 +2490,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>299</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>92</v>
@@ -2519,28 +2519,28 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>314</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>314</v>
@@ -2551,31 +2551,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
@@ -2583,31 +2583,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>323</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
@@ -2615,31 +2615,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>352</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2647,34 +2647,34 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>90</v>
@@ -2711,25 +2711,25 @@
         <v>179</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>188</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>91</v>
@@ -2741,264 +2741,264 @@
         <v>190</v>
       </c>
       <c r="Q1" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>92</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>193</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>197</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>97</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>352</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="M5" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>107</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>406</v>
@@ -3030,7 +3030,7 @@
         <v>411</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>412</v>
@@ -3045,7 +3045,7 @@
         <v>415</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>416</v>
@@ -3054,16 +3054,16 @@
         <v>417</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>418</v>
@@ -3075,7 +3075,7 @@
         <v>420</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U6" s="1" t="s">
         <v>421</v>
@@ -3105,26 +3105,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3132,15 +3132,15 @@
         <v>424</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3162,47 +3162,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>425</v>
+        <v>387</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>96</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>429</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>100</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>104</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>430</v>
+        <v>138</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>429</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3286,24 +3286,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>436</v>
@@ -3323,47 +3323,47 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>349</v>
+        <v>452</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>453</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>458</v>
@@ -3898,42 +3898,42 @@
         <v>148</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>160</v>
@@ -4085,25 +4085,25 @@
         <v>197</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>96</v>
@@ -4120,43 +4120,43 @@
         <v>191</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>197</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>100</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>102</v>
@@ -4173,43 +4173,43 @@
         <v>197</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>192</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>104</v>
@@ -4217,52 +4217,52 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>191</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>197</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>108</v>
@@ -4270,55 +4270,55 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4343,7 +4343,7 @@
         <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>91</v>
@@ -4357,19 +4357,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>96</v>
@@ -4377,19 +4377,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>100</v>
@@ -4397,19 +4397,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>104</v>
@@ -4417,19 +4417,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>108</v>
@@ -4437,19 +4437,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>112</v>
@@ -4477,57 +4477,57 @@
         <v>180</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>253</v>
+        <v>205</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>258</v>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>261</v>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>276</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>277</v>
@@ -4655,15 +4655,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>280</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>281</v>

--- a/example-data/dummydata-a2.xlsx
+++ b/example-data/dummydata-a2.xlsx
@@ -409,982 +409,982 @@
     <t>a2_auteursrechtHouder_1</t>
   </si>
   <si>
-    <t>2028-02-26</t>
+    <t>2009-09-05</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_3</t>
+  </si>
+  <si>
+    <t>a2_producent_1</t>
+  </si>
+  <si>
+    <t>2021-11-20T19:36:34.964Z</t>
+  </si>
+  <si>
+    <t>a2_taal_1</t>
+  </si>
+  <si>
+    <t>a2_uitgever_1</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_1</t>
+  </si>
+  <si>
+    <t>a2_versie_1</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_2</t>
+  </si>
+  <si>
+    <t>a2_auteur_2</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_2</t>
+  </si>
+  <si>
+    <t>2024-07-31</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_1</t>
+  </si>
+  <si>
+    <t>a2_producent_2</t>
+  </si>
+  <si>
+    <t>2029-12-22T13:16:22.589Z</t>
+  </si>
+  <si>
+    <t>a2_taal_2</t>
+  </si>
+  <si>
+    <t>a2_uitgever_2</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_2</t>
+  </si>
+  <si>
+    <t>a2_versie_2</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_3</t>
+  </si>
+  <si>
+    <t>a2_auteur_3</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_3</t>
+  </si>
+  <si>
+    <t>2006-04-26</t>
+  </si>
+  <si>
+    <t>a2_producent_3</t>
+  </si>
+  <si>
+    <t>2029-02-28T08:48:30.758Z</t>
+  </si>
+  <si>
+    <t>a2_taal_3</t>
+  </si>
+  <si>
+    <t>a2_uitgever_3</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_3</t>
+  </si>
+  <si>
+    <t>a2_versie_3</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_4</t>
+  </si>
+  <si>
+    <t>a2_auteur_4</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_4</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_5</t>
+  </si>
+  <si>
+    <t>a2_producent_4</t>
+  </si>
+  <si>
+    <t>2024-11-18T11:59:34.488Z</t>
+  </si>
+  <si>
+    <t>a2_taal_4</t>
+  </si>
+  <si>
+    <t>a2_uitgever_4</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_4</t>
+  </si>
+  <si>
+    <t>a2_versie_4</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_5</t>
+  </si>
+  <si>
+    <t>a2_auteur_5|a2_auteur_5b</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
+  </si>
+  <si>
+    <t>2013-08-20</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_4|a2/code/Licentie_2</t>
+  </si>
+  <si>
+    <t>a2_producent_5|a2_producent_5b</t>
+  </si>
+  <si>
+    <t>2007-09-10T12:55:59.017Z</t>
+  </si>
+  <si>
+    <t>a2_taal_5|a2_taal_5b</t>
+  </si>
+  <si>
+    <t>a2_uitgever_5|a2_uitgever_5b</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_5</t>
+  </si>
+  <si>
+    <t>a2_versie_5</t>
+  </si>
+  <si>
+    <t>bestaatUit</t>
+  </si>
+  <si>
+    <t>bron</t>
+  </si>
+  <si>
+    <t>competentie</t>
+  </si>
+  <si>
+    <t>doelgroep</t>
+  </si>
+  <si>
+    <t>gedefinieerdDoor</t>
+  </si>
+  <si>
+    <t>geldigheid</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>gerelateerdAan</t>
+  </si>
+  <si>
+    <t>heeftSpecialisatie</t>
+  </si>
+  <si>
+    <t>identificator</t>
+  </si>
+  <si>
+    <t>isBrederDan</t>
+  </si>
+  <si>
+    <t>isLidVan</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>onderwerp</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2_bron_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_1</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_5</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_1</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2_bron_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_2</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_2</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_2</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_2</t>
+  </si>
+  <si>
+    <t>a2_bron_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_3</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_2</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2_niveau_3</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_3</t>
+  </si>
+  <si>
+    <t>a2_bron_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_4</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_4</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_4</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2_bron_5|a2_bron_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_4|a2/code/Competentie_3</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1|a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2_niveau_5|a2_niveau_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
+  </si>
+  <si>
+    <t>a2_type_5|a2_type_5b</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_5</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_5</t>
+  </si>
+  <si>
+    <t>leeftijdstype</t>
+  </si>
+  <si>
+    <t>onderwijsniveau</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_1</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_2</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_2</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_3</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_4</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_5</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
+  </si>
+  <si>
+    <t>valuta</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_1</t>
+  </si>
+  <si>
+    <t>a2_valuta_1</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_2</t>
+  </si>
+  <si>
+    <t>a2_valuta_2</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_3</t>
+  </si>
+  <si>
+    <t>a2_valuta_3</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_4</t>
+  </si>
+  <si>
+    <t>a2_valuta_4</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_5</t>
+  </si>
+  <si>
+    <t>a2_valuta_5</t>
+  </si>
+  <si>
+    <t>toegekendDoor</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_1</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_4</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_4</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_5</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
+    <t>waarde</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_1</t>
+  </si>
+  <si>
+    <t>a2_eenheid_1</t>
+  </si>
+  <si>
+    <t>a2_waarde_1</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_2</t>
+  </si>
+  <si>
+    <t>a2_eenheid_2</t>
+  </si>
+  <si>
+    <t>a2_waarde_2</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_3</t>
+  </si>
+  <si>
+    <t>a2_eenheid_3</t>
+  </si>
+  <si>
+    <t>a2_waarde_3</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_4</t>
+  </si>
+  <si>
+    <t>a2_eenheid_4</t>
+  </si>
+  <si>
+    <t>a2_waarde_4</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_5</t>
+  </si>
+  <si>
+    <t>a2_eenheid_5</t>
+  </si>
+  <si>
+    <t>a2_waarde_5</t>
+  </si>
+  <si>
+    <t>draagtBijAanHetBehalenVan</t>
+  </si>
+  <si>
+    <t>heeftDeel</t>
+  </si>
+  <si>
+    <t>ingerichtDoor</t>
+  </si>
+  <si>
+    <t>isDeelVan</t>
+  </si>
+  <si>
+    <t>leermiddel</t>
+  </si>
+  <si>
+    <t>locatie</t>
+  </si>
+  <si>
+    <t>periode</t>
+  </si>
+  <si>
+    <t>specificatie</t>
+  </si>
+  <si>
+    <t>werklast</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4</t>
+  </si>
+  <si>
+    <t>a2_periode_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2_werklast_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2_periode_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2_periode_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_werklast_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_4</t>
+  </si>
+  <si>
+    <t>a2_periode_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_werklast_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_3|a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2|a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Adresvoorstelling_1|a2/code/Adresvoorstelling_2</t>
+  </si>
+  <si>
+    <t>a2_periode_5|a2_periode_5b</t>
+  </si>
+  <si>
+    <t>a2_werklast_5</t>
+  </si>
+  <si>
+    <t>contacturen</t>
+  </si>
+  <si>
+    <t>generalisatieVan</t>
+  </si>
+  <si>
+    <t>instructietaal</t>
+  </si>
+  <si>
+    <t>schrijftVoor</t>
+  </si>
+  <si>
+    <t>specialisatieVan</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_3</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1|a2/code/Openingsurenspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>benodigdMateriaal</t>
+  </si>
+  <si>
+    <t>dient</t>
+  </si>
+  <si>
+    <t>formaat</t>
+  </si>
+  <si>
+    <t>instructie</t>
+  </si>
+  <si>
+    <t>interactieType</t>
+  </si>
+  <si>
+    <t>kost</t>
+  </si>
+  <si>
+    <t>resultaat</t>
+  </si>
+  <si>
+    <t>sleutelwoord</t>
+  </si>
+  <si>
+    <t>toegankelijkheid</t>
+  </si>
+  <si>
+    <t>vereiste</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_4</t>
+  </si>
+  <si>
+    <t>a2_formaat_1</t>
+  </si>
+  <si>
+    <t>a2_instructie_1</t>
+  </si>
+  <si>
+    <t>a2_interactieType_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_5</t>
+  </si>
+  <si>
+    <t>a2_resultaat_1</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_1</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_1</t>
+  </si>
+  <si>
+    <t>a2_vereiste_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2_formaat_2</t>
+  </si>
+  <si>
+    <t>a2_instructie_2</t>
+  </si>
+  <si>
+    <t>a2_interactieType_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3</t>
+  </si>
+  <si>
+    <t>a2_resultaat_2</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_2</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_2</t>
+  </si>
+  <si>
+    <t>a2_vereiste_2</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_3</t>
+  </si>
+  <si>
+    <t>a2_formaat_3</t>
+  </si>
+  <si>
+    <t>a2_instructie_3</t>
+  </si>
+  <si>
+    <t>a2_interactieType_3</t>
+  </si>
+  <si>
+    <t>a2_resultaat_3</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_3</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_3</t>
+  </si>
+  <si>
+    <t>a2_vereiste_3</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_5</t>
+  </si>
+  <si>
+    <t>a2_formaat_4</t>
+  </si>
+  <si>
+    <t>a2_instructie_4</t>
+  </si>
+  <si>
+    <t>a2_interactieType_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_4</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_4</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_4</t>
+  </si>
+  <si>
+    <t>a2_vereiste_4</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2|a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_3|a2/code/Competentie_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2_formaat_5|a2_formaat_5b</t>
+  </si>
+  <si>
+    <t>a2_instructie_5</t>
+  </si>
+  <si>
+    <t>a2_interactieType_5|a2_interactieType_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_5|a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2_resultaat_5|a2_resultaat_5b</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_5</t>
+  </si>
+  <si>
+    <t>a2_vereiste_5|a2_vereiste_5b</t>
+  </si>
+  <si>
+    <t>onderdeelVan</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_5</t>
   </si>
   <si>
     <t>a2/code/Licentie_2</t>
   </si>
   <si>
-    <t>a2_producent_1</t>
-  </si>
-  <si>
-    <t>2007-10-03T01:45:59.468Z</t>
-  </si>
-  <si>
-    <t>a2_taal_1</t>
-  </si>
-  <si>
-    <t>a2_uitgever_1</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_1</t>
-  </si>
-  <si>
-    <t>a2_versie_1</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_2</t>
-  </si>
-  <si>
-    <t>a2_auteur_2</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_2</t>
-  </si>
-  <si>
-    <t>2029-05-21</t>
-  </si>
-  <si>
     <t>a2/code/Licentie_4</t>
   </si>
   <si>
-    <t>a2_producent_2</t>
-  </si>
-  <si>
-    <t>2002-12-28T20:00:37.958Z</t>
-  </si>
-  <si>
-    <t>a2_taal_2</t>
-  </si>
-  <si>
-    <t>a2_uitgever_2</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_2</t>
-  </si>
-  <si>
-    <t>a2_versie_2</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_3</t>
-  </si>
-  <si>
-    <t>a2_auteur_3</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_3</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2_producent_3</t>
-  </si>
-  <si>
-    <t>2009-07-13T22:58:43.915Z</t>
-  </si>
-  <si>
-    <t>a2_taal_3</t>
-  </si>
-  <si>
-    <t>a2_uitgever_3</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_3</t>
-  </si>
-  <si>
-    <t>a2_versie_3</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_4</t>
-  </si>
-  <si>
-    <t>a2_auteur_4</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_4</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>a2_producent_4</t>
-  </si>
-  <si>
-    <t>2012-12-31T21:21:00.473Z</t>
-  </si>
-  <si>
-    <t>a2_taal_4</t>
-  </si>
-  <si>
-    <t>a2_uitgever_4</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_4</t>
-  </si>
-  <si>
-    <t>a2_versie_4</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_5</t>
-  </si>
-  <si>
-    <t>a2_auteur_5|a2_auteur_5b</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
-  </si>
-  <si>
-    <t>2019-06-18</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_3|a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2_producent_5|a2_producent_5b</t>
-  </si>
-  <si>
-    <t>2030-08-24T04:52:17.103Z</t>
-  </si>
-  <si>
-    <t>a2_taal_5|a2_taal_5b</t>
-  </si>
-  <si>
-    <t>a2_uitgever_5|a2_uitgever_5b</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_5</t>
-  </si>
-  <si>
-    <t>a2_versie_5</t>
-  </si>
-  <si>
-    <t>bestaatUit</t>
-  </si>
-  <si>
-    <t>bron</t>
-  </si>
-  <si>
-    <t>competentie</t>
-  </si>
-  <si>
-    <t>doelgroep</t>
-  </si>
-  <si>
-    <t>gedefinieerdDoor</t>
-  </si>
-  <si>
-    <t>geldigheid</t>
-  </si>
-  <si>
-    <t>gelijkaardig</t>
-  </si>
-  <si>
-    <t>gerelateerdAan</t>
-  </si>
-  <si>
-    <t>heeftSpecialisatie</t>
-  </si>
-  <si>
-    <t>identificator</t>
-  </si>
-  <si>
-    <t>isBrederDan</t>
-  </si>
-  <si>
-    <t>isLidVan</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>onderwerp</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_bron_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_1</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_1</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_1</t>
-  </si>
-  <si>
-    <t>a2_bron_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_2</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_2</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_2</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_2</t>
-  </si>
-  <si>
-    <t>a2_bron_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_3</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_5</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_3</t>
-  </si>
-  <si>
-    <t>a2_niveau_3</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_3</t>
-  </si>
-  <si>
-    <t>a2_bron_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_5</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_4</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_4</t>
-  </si>
-  <si>
-    <t>a2_niveau_4</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2_bron_5|a2_bron_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_1|a2/code/Competentie_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_2|a2/code/DoelCollectie_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_5|a2_niveau_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
-  </si>
-  <si>
-    <t>a2_type_5|a2_type_5b</t>
-  </si>
-  <si>
-    <t>heeftLid</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_5</t>
-  </si>
-  <si>
-    <t>leeftijdstype</t>
-  </si>
-  <si>
-    <t>onderwijsniveau</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_1</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_1</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_2</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_2</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_3</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_4</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_4</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
-  </si>
-  <si>
-    <t>valuta</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_1</t>
-  </si>
-  <si>
-    <t>a2_valuta_1</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_2</t>
-  </si>
-  <si>
-    <t>a2_valuta_2</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_3</t>
-  </si>
-  <si>
-    <t>a2_valuta_3</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_4</t>
-  </si>
-  <si>
-    <t>a2_valuta_4</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_5</t>
-  </si>
-  <si>
-    <t>a2_valuta_5</t>
-  </si>
-  <si>
-    <t>toegekendDoor</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_1</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_3</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_3</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_5</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
-    <t>waarde</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_1</t>
-  </si>
-  <si>
-    <t>a2_eenheid_1</t>
-  </si>
-  <si>
-    <t>a2_waarde_1</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_2</t>
-  </si>
-  <si>
-    <t>a2_eenheid_2</t>
-  </si>
-  <si>
-    <t>a2_waarde_2</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_3</t>
-  </si>
-  <si>
-    <t>a2_eenheid_3</t>
-  </si>
-  <si>
-    <t>a2_waarde_3</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_4</t>
-  </si>
-  <si>
-    <t>a2_eenheid_4</t>
-  </si>
-  <si>
-    <t>a2_waarde_4</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_5</t>
-  </si>
-  <si>
-    <t>a2_eenheid_5</t>
-  </si>
-  <si>
-    <t>a2_waarde_5</t>
-  </si>
-  <si>
-    <t>draagtBijAanHetBehalenVan</t>
-  </si>
-  <si>
-    <t>heeftDeel</t>
-  </si>
-  <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
-    <t>isDeelVan</t>
-  </si>
-  <si>
-    <t>leermiddel</t>
-  </si>
-  <si>
-    <t>locatie</t>
-  </si>
-  <si>
-    <t>periode</t>
-  </si>
-  <si>
-    <t>specificatie</t>
-  </si>
-  <si>
-    <t>werklast</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2_periode_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_werklast_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2_periode_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4</t>
-  </si>
-  <si>
-    <t>a2_periode_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_4</t>
-  </si>
-  <si>
-    <t>a2_periode_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2_werklast_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5|a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1|a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Adresvoorstelling_5|a2/code/Adresvoorstelling_5</t>
-  </si>
-  <si>
-    <t>a2_periode_5|a2_periode_5b</t>
-  </si>
-  <si>
-    <t>a2_werklast_5</t>
-  </si>
-  <si>
-    <t>contacturen</t>
-  </si>
-  <si>
-    <t>generalisatieVan</t>
-  </si>
-  <si>
-    <t>instructietaal</t>
-  </si>
-  <si>
-    <t>schrijftVoor</t>
-  </si>
-  <si>
-    <t>specialisatieVan</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1</t>
+    <t>dagVanDeWeek</t>
+  </si>
+  <si>
+    <t>geldigTot</t>
+  </si>
+  <si>
+    <t>geldigVan</t>
+  </si>
+  <si>
+    <t>gesloten</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_1</t>
+  </si>
+  <si>
+    <t>2014-07-05T13:59:11.115Z</t>
+  </si>
+  <si>
+    <t>2014-08-06T00:09:11.465Z</t>
+  </si>
+  <si>
+    <t>08:50:44</t>
+  </si>
+  <si>
+    <t>16:05:22</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_2</t>
   </si>
   <si>
-    <t>a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_2</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_3</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_5|a2/code/Openingsurenspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4|a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>benodigdMateriaal</t>
-  </si>
-  <si>
-    <t>dient</t>
-  </si>
-  <si>
-    <t>formaat</t>
-  </si>
-  <si>
-    <t>instructie</t>
-  </si>
-  <si>
-    <t>interactieType</t>
-  </si>
-  <si>
-    <t>kost</t>
-  </si>
-  <si>
-    <t>resultaat</t>
-  </si>
-  <si>
-    <t>sleutelwoord</t>
-  </si>
-  <si>
-    <t>toegankelijkheid</t>
-  </si>
-  <si>
-    <t>vereiste</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_5</t>
-  </si>
-  <si>
-    <t>a2_formaat_1</t>
-  </si>
-  <si>
-    <t>a2_instructie_1</t>
-  </si>
-  <si>
-    <t>a2_interactieType_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_5</t>
-  </si>
-  <si>
-    <t>a2_resultaat_1</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_1</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_1</t>
-  </si>
-  <si>
-    <t>a2_vereiste_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2_formaat_2</t>
-  </si>
-  <si>
-    <t>a2_instructie_2</t>
-  </si>
-  <si>
-    <t>a2_interactieType_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2_resultaat_2</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_2</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_2</t>
-  </si>
-  <si>
-    <t>a2_vereiste_2</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_3</t>
-  </si>
-  <si>
-    <t>a2_formaat_3</t>
-  </si>
-  <si>
-    <t>a2_instructie_3</t>
-  </si>
-  <si>
-    <t>a2_interactieType_3</t>
-  </si>
-  <si>
-    <t>a2_resultaat_3</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_3</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_3</t>
-  </si>
-  <si>
-    <t>a2_vereiste_3</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_3</t>
-  </si>
-  <si>
-    <t>a2_formaat_4</t>
-  </si>
-  <si>
-    <t>a2_instructie_4</t>
-  </si>
-  <si>
-    <t>a2_interactieType_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_4</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_4</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_4</t>
-  </si>
-  <si>
-    <t>a2_vereiste_4</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2|a2/code/LeermiddelElement_5</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_3|a2/code/Competentie_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_formaat_5|a2_formaat_5b</t>
-  </si>
-  <si>
-    <t>a2_instructie_5</t>
-  </si>
-  <si>
-    <t>a2_interactieType_5|a2_interactieType_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_3|a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2_resultaat_5|a2_resultaat_5b</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_5</t>
-  </si>
-  <si>
-    <t>a2_vereiste_5|a2_vereiste_5b</t>
-  </si>
-  <si>
-    <t>onderdeelVan</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_3</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_5</t>
-  </si>
-  <si>
-    <t>dagVanDeWeek</t>
-  </si>
-  <si>
-    <t>geldigTot</t>
-  </si>
-  <si>
-    <t>geldigVan</t>
-  </si>
-  <si>
-    <t>gesloten</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_1</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_1</t>
-  </si>
-  <si>
-    <t>2002-10-22T00:56:42.762Z</t>
-  </si>
-  <si>
-    <t>2029-01-29T06:29:01.072Z</t>
-  </si>
-  <si>
-    <t>11:40:50</t>
-  </si>
-  <si>
-    <t>07:03:14</t>
-  </si>
-  <si>
     <t>http://example.com/au/dagVanDeWeek_2</t>
   </si>
   <si>
-    <t>2024-07-18T21:35:49.315Z</t>
-  </si>
-  <si>
-    <t>2016-08-21T14:05:54.029Z</t>
-  </si>
-  <si>
-    <t>14:51:59</t>
-  </si>
-  <si>
-    <t>08:56:04</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_3</t>
+    <t>2004-01-09T08:01:53.568Z</t>
+  </si>
+  <si>
+    <t>2008-11-06T13:57:44.027Z</t>
+  </si>
+  <si>
+    <t>14:21:59</t>
+  </si>
+  <si>
+    <t>22:15:02</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_3</t>
   </si>
   <si>
-    <t>2025-04-24T09:32:43.191Z</t>
-  </si>
-  <si>
-    <t>2001-01-13T16:41:53.054Z</t>
-  </si>
-  <si>
-    <t>17:27:03</t>
-  </si>
-  <si>
-    <t>13:49:49</t>
+    <t>2005-05-01T19:12:00.133Z</t>
+  </si>
+  <si>
+    <t>2002-05-29T11:44:37.101Z</t>
+  </si>
+  <si>
+    <t>10:52:35</t>
+  </si>
+  <si>
+    <t>22:47:32</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_4</t>
@@ -1393,31 +1393,31 @@
     <t>http://example.com/au/dagVanDeWeek_4</t>
   </si>
   <si>
-    <t>2016-04-05T02:38:48.513Z</t>
-  </si>
-  <si>
-    <t>2024-08-23T02:57:00.428Z</t>
-  </si>
-  <si>
-    <t>03:40:25</t>
-  </si>
-  <si>
-    <t>19:20:40</t>
+    <t>2017-11-25T21:05:07.844Z</t>
+  </si>
+  <si>
+    <t>2011-07-04T06:28:57.468Z</t>
+  </si>
+  <si>
+    <t>22:14:29</t>
+  </si>
+  <si>
+    <t>12:54:12</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_5</t>
   </si>
   <si>
-    <t>2022-08-21T19:22:45.077Z</t>
-  </si>
-  <si>
-    <t>2027-07-28T15:26:21.240Z</t>
-  </si>
-  <si>
-    <t>19:08:04</t>
-  </si>
-  <si>
-    <t>05:49:49</t>
+    <t>2005-08-08T06:22:30.912Z</t>
+  </si>
+  <si>
+    <t>2027-07-17T13:23:53.074Z</t>
+  </si>
+  <si>
+    <t>14:08:21</t>
+  </si>
+  <si>
+    <t>10:53:54</t>
   </si>
   <si>
     <t>tot</t>
@@ -2304,171 +2304,171 @@
         <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>322</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>324</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -2490,28 +2490,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>299</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>92</v>
@@ -2519,31 +2519,31 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>345</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
@@ -2551,31 +2551,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>348</v>
+        <v>311</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
@@ -2583,31 +2583,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>345</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>323</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
@@ -2615,31 +2615,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>352</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2647,34 +2647,34 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>90</v>
@@ -2711,25 +2711,25 @@
         <v>179</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>188</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>91</v>
@@ -2741,344 +2741,344 @@
         <v>190</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>92</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>193</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>352</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>107</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="U6" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3100,12 +3100,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>323</v>
@@ -3113,34 +3113,34 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>424</v>
+        <v>374</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3162,47 +3162,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>426</v>
+        <v>388</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>96</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>127</v>
+        <v>429</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>100</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>428</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>104</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>429</v>
+        <v>159</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3286,24 +3286,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>435</v>
+        <v>351</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>436</v>
@@ -3323,27 +3323,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>345</v>
+        <v>441</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>446</v>
+        <v>345</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>447</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>458</v>
@@ -3898,42 +3898,42 @@
         <v>148</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>160</v>
@@ -4070,7 +4070,7 @@
         <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>194</v>
@@ -4085,25 +4085,25 @@
         <v>197</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>96</v>
@@ -4111,52 +4111,52 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>100</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>102</v>
@@ -4173,43 +4173,43 @@
         <v>197</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>104</v>
@@ -4217,52 +4217,52 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>192</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>197</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>108</v>
@@ -4270,55 +4270,55 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4343,7 +4343,7 @@
         <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>91</v>
@@ -4357,19 +4357,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>96</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>197</v>
@@ -4389,7 +4389,7 @@
         <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>100</v>
@@ -4397,19 +4397,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>104</v>
@@ -4417,19 +4417,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>108</v>
@@ -4437,19 +4437,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>112</v>
@@ -4477,80 +4477,80 @@
         <v>180</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4572,47 +4572,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -4634,36 +4634,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>280</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>281</v>

--- a/example-data/dummydata-a2.xlsx
+++ b/example-data/dummydata-a2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="510">
   <si>
     <t>CODE</t>
   </si>
@@ -409,1015 +409,1009 @@
     <t>a2_auteursrechtHouder_1</t>
   </si>
   <si>
-    <t>2009-09-05</t>
+    <t>2014-05-02</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_5</t>
+  </si>
+  <si>
+    <t>a2_producent_1</t>
+  </si>
+  <si>
+    <t>2020-05-11T16:47:58.422Z</t>
+  </si>
+  <si>
+    <t>a2_taal_1</t>
+  </si>
+  <si>
+    <t>a2_uitgever_1</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_1</t>
+  </si>
+  <si>
+    <t>a2_versie_1</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_2</t>
+  </si>
+  <si>
+    <t>a2_auteur_2</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_2</t>
+  </si>
+  <si>
+    <t>2014-06-05</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_2</t>
+  </si>
+  <si>
+    <t>a2_producent_2</t>
+  </si>
+  <si>
+    <t>2023-08-08T03:09:58.027Z</t>
+  </si>
+  <si>
+    <t>a2_taal_2</t>
+  </si>
+  <si>
+    <t>a2_uitgever_2</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_2</t>
+  </si>
+  <si>
+    <t>a2_versie_2</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_3</t>
+  </si>
+  <si>
+    <t>a2_auteur_3</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_3</t>
+  </si>
+  <si>
+    <t>2022-02-10</t>
+  </si>
+  <si>
+    <t>a2_producent_3</t>
+  </si>
+  <si>
+    <t>2023-10-14T23:17:00.950Z</t>
+  </si>
+  <si>
+    <t>a2_taal_3</t>
+  </si>
+  <si>
+    <t>a2_uitgever_3</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_3</t>
+  </si>
+  <si>
+    <t>a2_versie_3</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_4</t>
+  </si>
+  <si>
+    <t>a2_auteur_4</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_4</t>
+  </si>
+  <si>
+    <t>2017-10-01</t>
   </si>
   <si>
     <t>a2/code/Licentie_3</t>
   </si>
   <si>
-    <t>a2_producent_1</t>
-  </si>
-  <si>
-    <t>2021-11-20T19:36:34.964Z</t>
-  </si>
-  <si>
-    <t>a2_taal_1</t>
-  </si>
-  <si>
-    <t>a2_uitgever_1</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_1</t>
-  </si>
-  <si>
-    <t>a2_versie_1</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_2</t>
-  </si>
-  <si>
-    <t>a2_auteur_2</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_2</t>
-  </si>
-  <si>
-    <t>2024-07-31</t>
+    <t>a2_producent_4</t>
+  </si>
+  <si>
+    <t>2006-10-19T23:59:43.710Z</t>
+  </si>
+  <si>
+    <t>a2_taal_4</t>
+  </si>
+  <si>
+    <t>a2_uitgever_4</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_4</t>
+  </si>
+  <si>
+    <t>a2_versie_4</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_5</t>
+  </si>
+  <si>
+    <t>a2_auteur_5|a2_auteur_5b</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
+  </si>
+  <si>
+    <t>2006-03-28</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_5|a2/code/Licentie_5</t>
+  </si>
+  <si>
+    <t>a2_producent_5|a2_producent_5b</t>
+  </si>
+  <si>
+    <t>2011-09-20T09:59:04.506Z</t>
+  </si>
+  <si>
+    <t>a2_taal_5|a2_taal_5b</t>
+  </si>
+  <si>
+    <t>a2_uitgever_5|a2_uitgever_5b</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_5</t>
+  </si>
+  <si>
+    <t>a2_versie_5</t>
+  </si>
+  <si>
+    <t>bestaatUit</t>
+  </si>
+  <si>
+    <t>bron</t>
+  </si>
+  <si>
+    <t>competentie</t>
+  </si>
+  <si>
+    <t>doelgroep</t>
+  </si>
+  <si>
+    <t>gedefinieerdDoor</t>
+  </si>
+  <si>
+    <t>geldigheid</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>gerelateerdAan</t>
+  </si>
+  <si>
+    <t>heeftSpecialisatie</t>
+  </si>
+  <si>
+    <t>identificator</t>
+  </si>
+  <si>
+    <t>isBrederDan</t>
+  </si>
+  <si>
+    <t>isLidVan</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>onderwerp</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2_bron_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_1</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_1</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_1</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_1</t>
+  </si>
+  <si>
+    <t>a2_bron_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_2</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_2</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_2</t>
+  </si>
+  <si>
+    <t>a2_bron_3</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_3</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_3</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_3</t>
+  </si>
+  <si>
+    <t>a2_bron_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_4</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2_niveau_4</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2_bron_5|a2_bron_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_4|a2/code/Competentie_2</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3|a2/code/DoelCollectie_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_5|a2_niveau_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
+  </si>
+  <si>
+    <t>a2_type_5|a2_type_5b</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_5</t>
+  </si>
+  <si>
+    <t>leeftijdstype</t>
+  </si>
+  <si>
+    <t>onderwijsniveau</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_1</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_1</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_2</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_3</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_4</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_5</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
+  </si>
+  <si>
+    <t>valuta</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_1</t>
+  </si>
+  <si>
+    <t>a2_valuta_1</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_2</t>
+  </si>
+  <si>
+    <t>a2_valuta_2</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_3</t>
+  </si>
+  <si>
+    <t>a2_valuta_3</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_4</t>
+  </si>
+  <si>
+    <t>a2_valuta_4</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_5</t>
+  </si>
+  <si>
+    <t>a2_valuta_5</t>
+  </si>
+  <si>
+    <t>toegekendDoor</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_1</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_2</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_4</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_5</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
+    <t>waarde</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_1</t>
+  </si>
+  <si>
+    <t>a2_eenheid_1</t>
+  </si>
+  <si>
+    <t>a2_waarde_1</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_2</t>
+  </si>
+  <si>
+    <t>a2_eenheid_2</t>
+  </si>
+  <si>
+    <t>a2_waarde_2</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_3</t>
+  </si>
+  <si>
+    <t>a2_eenheid_3</t>
+  </si>
+  <si>
+    <t>a2_waarde_3</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_4</t>
+  </si>
+  <si>
+    <t>a2_eenheid_4</t>
+  </si>
+  <si>
+    <t>a2_waarde_4</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_5</t>
+  </si>
+  <si>
+    <t>a2_eenheid_5</t>
+  </si>
+  <si>
+    <t>a2_waarde_5</t>
+  </si>
+  <si>
+    <t>draagtBijAanHetBehalenVan</t>
+  </si>
+  <si>
+    <t>heeftDeel</t>
+  </si>
+  <si>
+    <t>ingerichtDoor</t>
+  </si>
+  <si>
+    <t>isDeelVan</t>
+  </si>
+  <si>
+    <t>leermiddel</t>
+  </si>
+  <si>
+    <t>locatie</t>
+  </si>
+  <si>
+    <t>periode</t>
+  </si>
+  <si>
+    <t>specificatie</t>
+  </si>
+  <si>
+    <t>werklast</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2_periode_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_werklast_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2_periode_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_werklast_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2_periode_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2_werklast_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4</t>
+  </si>
+  <si>
+    <t>a2_periode_4</t>
+  </si>
+  <si>
+    <t>a2_werklast_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1|a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4|a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_1|a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Adresvoorstelling_4|a2/code/Adresvoorstelling_1</t>
+  </si>
+  <si>
+    <t>a2_periode_5|a2_periode_5b</t>
+  </si>
+  <si>
+    <t>a2_werklast_5</t>
+  </si>
+  <si>
+    <t>contacturen</t>
+  </si>
+  <si>
+    <t>generalisatieVan</t>
+  </si>
+  <si>
+    <t>instructietaal</t>
+  </si>
+  <si>
+    <t>schrijftVoor</t>
+  </si>
+  <si>
+    <t>specialisatieVan</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_4|a2/code/Openingsurenspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5|a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>benodigdMateriaal</t>
+  </si>
+  <si>
+    <t>dient</t>
+  </si>
+  <si>
+    <t>formaat</t>
+  </si>
+  <si>
+    <t>instructie</t>
+  </si>
+  <si>
+    <t>interactieType</t>
+  </si>
+  <si>
+    <t>kost</t>
+  </si>
+  <si>
+    <t>resultaat</t>
+  </si>
+  <si>
+    <t>sleutelwoord</t>
+  </si>
+  <si>
+    <t>toegankelijkheid</t>
+  </si>
+  <si>
+    <t>vereiste</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_3</t>
+  </si>
+  <si>
+    <t>a2_formaat_1</t>
+  </si>
+  <si>
+    <t>a2_instructie_1</t>
+  </si>
+  <si>
+    <t>a2_interactieType_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2_resultaat_1</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_1</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_1</t>
+  </si>
+  <si>
+    <t>a2_vereiste_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_4</t>
+  </si>
+  <si>
+    <t>a2_formaat_2</t>
+  </si>
+  <si>
+    <t>a2_instructie_2</t>
+  </si>
+  <si>
+    <t>a2_interactieType_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2_resultaat_2</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_2</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_2</t>
+  </si>
+  <si>
+    <t>a2_vereiste_2</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_5</t>
+  </si>
+  <si>
+    <t>a2_formaat_3</t>
+  </si>
+  <si>
+    <t>a2_instructie_3</t>
+  </si>
+  <si>
+    <t>a2_interactieType_3</t>
+  </si>
+  <si>
+    <t>a2_resultaat_3</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_3</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_3</t>
+  </si>
+  <si>
+    <t>a2_vereiste_3</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_4</t>
+  </si>
+  <si>
+    <t>a2_formaat_4</t>
+  </si>
+  <si>
+    <t>a2_instructie_4</t>
+  </si>
+  <si>
+    <t>a2_interactieType_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_4</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_4</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_4</t>
+  </si>
+  <si>
+    <t>a2_vereiste_4</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_1|a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_2|a2/code/Competentie_1</t>
+  </si>
+  <si>
+    <t>a2_formaat_5|a2_formaat_5b</t>
+  </si>
+  <si>
+    <t>a2_instructie_5</t>
+  </si>
+  <si>
+    <t>a2_interactieType_5|a2_interactieType_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_2|a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2_resultaat_5|a2_resultaat_5b</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_5</t>
+  </si>
+  <si>
+    <t>a2_vereiste_5|a2_vereiste_5b</t>
+  </si>
+  <si>
+    <t>onderdeelVan</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_2</t>
   </si>
   <si>
     <t>a2/code/Licentie_1</t>
   </si>
   <si>
-    <t>a2_producent_2</t>
-  </si>
-  <si>
-    <t>2029-12-22T13:16:22.589Z</t>
-  </si>
-  <si>
-    <t>a2_taal_2</t>
-  </si>
-  <si>
-    <t>a2_uitgever_2</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_2</t>
-  </si>
-  <si>
-    <t>a2_versie_2</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_3</t>
-  </si>
-  <si>
-    <t>a2_auteur_3</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_3</t>
-  </si>
-  <si>
-    <t>2006-04-26</t>
-  </si>
-  <si>
-    <t>a2_producent_3</t>
-  </si>
-  <si>
-    <t>2029-02-28T08:48:30.758Z</t>
-  </si>
-  <si>
-    <t>a2_taal_3</t>
-  </si>
-  <si>
-    <t>a2_uitgever_3</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_3</t>
-  </si>
-  <si>
-    <t>a2_versie_3</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_4</t>
-  </si>
-  <si>
-    <t>a2_auteur_4</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_4</t>
-  </si>
-  <si>
-    <t>2021-09-24</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_5</t>
-  </si>
-  <si>
-    <t>a2_producent_4</t>
-  </si>
-  <si>
-    <t>2024-11-18T11:59:34.488Z</t>
-  </si>
-  <si>
-    <t>a2_taal_4</t>
-  </si>
-  <si>
-    <t>a2_uitgever_4</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_4</t>
-  </si>
-  <si>
-    <t>a2_versie_4</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_5</t>
-  </si>
-  <si>
-    <t>a2_auteur_5|a2_auteur_5b</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
-  </si>
-  <si>
-    <t>2013-08-20</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_4|a2/code/Licentie_2</t>
-  </si>
-  <si>
-    <t>a2_producent_5|a2_producent_5b</t>
-  </si>
-  <si>
-    <t>2007-09-10T12:55:59.017Z</t>
-  </si>
-  <si>
-    <t>a2_taal_5|a2_taal_5b</t>
-  </si>
-  <si>
-    <t>a2_uitgever_5|a2_uitgever_5b</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_5</t>
-  </si>
-  <si>
-    <t>a2_versie_5</t>
-  </si>
-  <si>
-    <t>bestaatUit</t>
-  </si>
-  <si>
-    <t>bron</t>
-  </si>
-  <si>
-    <t>competentie</t>
-  </si>
-  <si>
-    <t>doelgroep</t>
-  </si>
-  <si>
-    <t>gedefinieerdDoor</t>
-  </si>
-  <si>
-    <t>geldigheid</t>
-  </si>
-  <si>
-    <t>gelijkaardig</t>
-  </si>
-  <si>
-    <t>gerelateerdAan</t>
-  </si>
-  <si>
-    <t>heeftSpecialisatie</t>
-  </si>
-  <si>
-    <t>identificator</t>
-  </si>
-  <si>
-    <t>isBrederDan</t>
-  </si>
-  <si>
-    <t>isLidVan</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>onderwerp</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_bron_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_1</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_5</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_1</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_bron_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_2</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_2</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_2</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_2</t>
-  </si>
-  <si>
-    <t>a2_bron_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_3</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_2</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_4</t>
-  </si>
-  <si>
-    <t>a2_niveau_3</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_3</t>
-  </si>
-  <si>
-    <t>a2_bron_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_4</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_4</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_4</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_bron_5|a2_bron_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_4|a2/code/Competentie_3</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1|a2/code/DoelCollectie_4</t>
-  </si>
-  <si>
-    <t>a2_niveau_5|a2_niveau_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
-  </si>
-  <si>
-    <t>a2_type_5|a2_type_5b</t>
-  </si>
-  <si>
-    <t>heeftLid</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_3</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_5</t>
-  </si>
-  <si>
-    <t>leeftijdstype</t>
-  </si>
-  <si>
-    <t>onderwijsniveau</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_1</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_2</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_2</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_3</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_4</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_5</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
-  </si>
-  <si>
-    <t>valuta</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_1</t>
-  </si>
-  <si>
-    <t>a2_valuta_1</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_2</t>
-  </si>
-  <si>
-    <t>a2_valuta_2</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_3</t>
-  </si>
-  <si>
-    <t>a2_valuta_3</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_4</t>
-  </si>
-  <si>
-    <t>a2_valuta_4</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_5</t>
-  </si>
-  <si>
-    <t>a2_valuta_5</t>
-  </si>
-  <si>
-    <t>toegekendDoor</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_1</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_3</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_5</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
-    <t>waarde</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_1</t>
-  </si>
-  <si>
-    <t>a2_eenheid_1</t>
-  </si>
-  <si>
-    <t>a2_waarde_1</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_2</t>
-  </si>
-  <si>
-    <t>a2_eenheid_2</t>
-  </si>
-  <si>
-    <t>a2_waarde_2</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_3</t>
-  </si>
-  <si>
-    <t>a2_eenheid_3</t>
-  </si>
-  <si>
-    <t>a2_waarde_3</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_4</t>
-  </si>
-  <si>
-    <t>a2_eenheid_4</t>
-  </si>
-  <si>
-    <t>a2_waarde_4</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_5</t>
-  </si>
-  <si>
-    <t>a2_eenheid_5</t>
-  </si>
-  <si>
-    <t>a2_waarde_5</t>
-  </si>
-  <si>
-    <t>draagtBijAanHetBehalenVan</t>
-  </si>
-  <si>
-    <t>heeftDeel</t>
-  </si>
-  <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
-    <t>isDeelVan</t>
-  </si>
-  <si>
-    <t>leermiddel</t>
-  </si>
-  <si>
-    <t>locatie</t>
-  </si>
-  <si>
-    <t>periode</t>
-  </si>
-  <si>
-    <t>specificatie</t>
-  </si>
-  <si>
-    <t>werklast</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4</t>
-  </si>
-  <si>
-    <t>a2_periode_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2_werklast_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2_periode_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2_periode_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_werklast_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_4</t>
-  </si>
-  <si>
-    <t>a2_periode_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_werklast_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_3|a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_2|a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Adresvoorstelling_1|a2/code/Adresvoorstelling_2</t>
-  </si>
-  <si>
-    <t>a2_periode_5|a2_periode_5b</t>
-  </si>
-  <si>
-    <t>a2_werklast_5</t>
-  </si>
-  <si>
-    <t>contacturen</t>
-  </si>
-  <si>
-    <t>generalisatieVan</t>
-  </si>
-  <si>
-    <t>instructietaal</t>
-  </si>
-  <si>
-    <t>schrijftVoor</t>
-  </si>
-  <si>
-    <t>specialisatieVan</t>
+    <t>a2/code/Licentie_4</t>
+  </si>
+  <si>
+    <t>dagVanDeWeek</t>
+  </si>
+  <si>
+    <t>geldigTot</t>
+  </si>
+  <si>
+    <t>geldigVan</t>
+  </si>
+  <si>
+    <t>gesloten</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_1</t>
+  </si>
+  <si>
+    <t>2018-06-04T14:27:36.396Z</t>
+  </si>
+  <si>
+    <t>2029-03-07T05:58:13.880Z</t>
+  </si>
+  <si>
+    <t>11:05:38</t>
+  </si>
+  <si>
+    <t>19:53:48</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_2</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_2</t>
+  </si>
+  <si>
+    <t>2025-11-20T23:52:58.245Z</t>
+  </si>
+  <si>
+    <t>2021-10-14T09:31:18.438Z</t>
+  </si>
+  <si>
+    <t>20:06:02</t>
+  </si>
+  <si>
+    <t>16:49:58</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_3</t>
   </si>
   <si>
-    <t>a2_instructietaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_2</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_3</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_1|a2/code/Openingsurenspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>benodigdMateriaal</t>
-  </si>
-  <si>
-    <t>dient</t>
-  </si>
-  <si>
-    <t>formaat</t>
-  </si>
-  <si>
-    <t>instructie</t>
-  </si>
-  <si>
-    <t>interactieType</t>
-  </si>
-  <si>
-    <t>kost</t>
-  </si>
-  <si>
-    <t>resultaat</t>
-  </si>
-  <si>
-    <t>sleutelwoord</t>
-  </si>
-  <si>
-    <t>toegankelijkheid</t>
-  </si>
-  <si>
-    <t>vereiste</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2_formaat_1</t>
-  </si>
-  <si>
-    <t>a2_instructie_1</t>
-  </si>
-  <si>
-    <t>a2_interactieType_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_5</t>
-  </si>
-  <si>
-    <t>a2_resultaat_1</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_1</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_1</t>
-  </si>
-  <si>
-    <t>a2_vereiste_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2_formaat_2</t>
-  </si>
-  <si>
-    <t>a2_instructie_2</t>
-  </si>
-  <si>
-    <t>a2_interactieType_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_3</t>
-  </si>
-  <si>
-    <t>a2_resultaat_2</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_2</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_2</t>
-  </si>
-  <si>
-    <t>a2_vereiste_2</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_3</t>
-  </si>
-  <si>
-    <t>a2_formaat_3</t>
-  </si>
-  <si>
-    <t>a2_instructie_3</t>
-  </si>
-  <si>
-    <t>a2_interactieType_3</t>
-  </si>
-  <si>
-    <t>a2_resultaat_3</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_3</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_3</t>
-  </si>
-  <si>
-    <t>a2_vereiste_3</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_5</t>
-  </si>
-  <si>
-    <t>a2_formaat_4</t>
-  </si>
-  <si>
-    <t>a2_instructie_4</t>
-  </si>
-  <si>
-    <t>a2_interactieType_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_4</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_4</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_4</t>
-  </si>
-  <si>
-    <t>a2_vereiste_4</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2|a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_3|a2/code/Competentie_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_formaat_5|a2_formaat_5b</t>
-  </si>
-  <si>
-    <t>a2_instructie_5</t>
-  </si>
-  <si>
-    <t>a2_interactieType_5|a2_interactieType_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_5|a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2_resultaat_5|a2_resultaat_5b</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_5</t>
-  </si>
-  <si>
-    <t>a2_vereiste_5|a2_vereiste_5b</t>
-  </si>
-  <si>
-    <t>onderdeelVan</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_3</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_2</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_4</t>
-  </si>
-  <si>
-    <t>dagVanDeWeek</t>
-  </si>
-  <si>
-    <t>geldigTot</t>
-  </si>
-  <si>
-    <t>geldigVan</t>
-  </si>
-  <si>
-    <t>gesloten</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_1</t>
-  </si>
-  <si>
-    <t>2014-07-05T13:59:11.115Z</t>
-  </si>
-  <si>
-    <t>2014-08-06T00:09:11.465Z</t>
-  </si>
-  <si>
-    <t>08:50:44</t>
-  </si>
-  <si>
-    <t>16:05:22</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_2</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_2</t>
-  </si>
-  <si>
-    <t>2004-01-09T08:01:53.568Z</t>
-  </si>
-  <si>
-    <t>2008-11-06T13:57:44.027Z</t>
-  </si>
-  <si>
-    <t>14:21:59</t>
-  </si>
-  <si>
-    <t>22:15:02</t>
-  </si>
-  <si>
     <t>http://example.com/au/dagVanDeWeek_3</t>
   </si>
   <si>
-    <t>2005-05-01T19:12:00.133Z</t>
-  </si>
-  <si>
-    <t>2002-05-29T11:44:37.101Z</t>
-  </si>
-  <si>
-    <t>10:52:35</t>
-  </si>
-  <si>
-    <t>22:47:32</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_4</t>
+    <t>2024-12-30T15:20:36.799Z</t>
+  </si>
+  <si>
+    <t>2026-01-26T17:09:34.900Z</t>
+  </si>
+  <si>
+    <t>14:02:36</t>
+  </si>
+  <si>
+    <t>00:59:06</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_4</t>
   </si>
   <si>
-    <t>2017-11-25T21:05:07.844Z</t>
-  </si>
-  <si>
-    <t>2011-07-04T06:28:57.468Z</t>
-  </si>
-  <si>
-    <t>22:14:29</t>
-  </si>
-  <si>
-    <t>12:54:12</t>
+    <t>2006-02-08T00:12:23.233Z</t>
+  </si>
+  <si>
+    <t>2000-10-05T01:31:02.846Z</t>
+  </si>
+  <si>
+    <t>08:57:41</t>
+  </si>
+  <si>
+    <t>14:03:20</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_5</t>
   </si>
   <si>
-    <t>2005-08-08T06:22:30.912Z</t>
-  </si>
-  <si>
-    <t>2027-07-17T13:23:53.074Z</t>
-  </si>
-  <si>
-    <t>14:08:21</t>
-  </si>
-  <si>
-    <t>10:53:54</t>
+    <t>2020-01-31T11:15:09.978Z</t>
+  </si>
+  <si>
+    <t>2029-07-22T14:49:56.409Z</t>
+  </si>
+  <si>
+    <t>00:32:45</t>
+  </si>
+  <si>
+    <t>11:16:02</t>
   </si>
   <si>
     <t>tot</t>
@@ -2301,133 +2295,133 @@
         <v>308</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>328</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2438,37 +2432,37 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -2490,28 +2484,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>299</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>92</v>
@@ -2519,31 +2513,31 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>346</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
@@ -2551,31 +2545,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
@@ -2583,31 +2577,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>350</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
@@ -2615,31 +2609,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2647,7 +2641,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>354</v>
@@ -2674,7 +2668,7 @@
         <v>361</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2720,7 +2714,7 @@
         <v>365</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>366</v>
@@ -2758,43 +2752,43 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>193</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>191</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>346</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>95</v>
@@ -2806,107 +2800,107 @@
         <v>201</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>394</v>
@@ -2921,10 +2915,10 @@
         <v>396</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>103</v>
@@ -2953,7 +2947,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>401</v>
@@ -2962,34 +2956,34 @@
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>218</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="L5" s="1" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>107</v>
@@ -3001,84 +2995,84 @@
         <v>223</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>358</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3100,47 +3094,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -3162,47 +3156,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>426</v>
+        <v>387</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>427</v>
+        <v>377</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>378</v>
+        <v>425</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -3229,7 +3223,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>427</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>96</v>
@@ -3237,7 +3231,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>429</v>
+        <v>138</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>100</v>
@@ -3245,7 +3239,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>104</v>
@@ -3253,7 +3247,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
@@ -3261,10 +3255,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3286,119 +3280,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3420,65 +3414,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -3497,63 +3491,63 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -3561,13 +3555,13 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -3575,13 +3569,13 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -3589,13 +3583,13 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -3603,13 +3597,13 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -3629,42 +3623,42 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -3898,7 +3892,7 @@
         <v>148</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>149</v>
@@ -4070,7 +4064,7 @@
         <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>194</v>
@@ -4085,16 +4079,16 @@
         <v>197</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>198</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>199</v>
@@ -4111,7 +4105,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>98</v>
@@ -4120,43 +4114,43 @@
         <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>100</v>
@@ -4164,22 +4158,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>212</v>
@@ -4188,13 +4182,13 @@
         <v>213</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>191</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>214</v>
@@ -4217,22 +4211,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>218</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>219</v>
@@ -4241,22 +4235,22 @@
         <v>220</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="L5" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>222</v>
@@ -4270,55 +4264,55 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4343,7 +4337,7 @@
         <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>91</v>
@@ -4357,13 +4351,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>95</v>
@@ -4377,19 +4371,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>100</v>
@@ -4403,7 +4397,7 @@
         <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>103</v>
@@ -4417,13 +4411,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>107</v>
@@ -4437,19 +4431,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>112</v>
@@ -4477,15 +4471,15 @@
         <v>180</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>246</v>
@@ -4499,21 +4493,21 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>253</v>
@@ -4527,7 +4521,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>256</v>
@@ -4639,7 +4633,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>275</v>
@@ -4647,23 +4641,23 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>279</v>
+        <v>214</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>280</v>
@@ -4671,7 +4665,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>281</v>

--- a/example-data/dummydata-a2.xlsx
+++ b/example-data/dummydata-a2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="509">
   <si>
     <t>CODE</t>
   </si>
@@ -409,1009 +409,1006 @@
     <t>a2_auteursrechtHouder_1</t>
   </si>
   <si>
-    <t>2014-05-02</t>
+    <t>2010-05-18</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_3</t>
+  </si>
+  <si>
+    <t>a2_producent_1</t>
+  </si>
+  <si>
+    <t>2000-05-07T09:41:38.431Z</t>
+  </si>
+  <si>
+    <t>a2_taal_1</t>
+  </si>
+  <si>
+    <t>a2_uitgever_1</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_1</t>
+  </si>
+  <si>
+    <t>a2_versie_1</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_2</t>
+  </si>
+  <si>
+    <t>a2_auteur_2</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_2</t>
+  </si>
+  <si>
+    <t>2001-10-11</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_1</t>
+  </si>
+  <si>
+    <t>a2_producent_2</t>
+  </si>
+  <si>
+    <t>2013-06-07T07:02:06.954Z</t>
+  </si>
+  <si>
+    <t>a2_taal_2</t>
+  </si>
+  <si>
+    <t>a2_uitgever_2</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_2</t>
+  </si>
+  <si>
+    <t>a2_versie_2</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_3</t>
+  </si>
+  <si>
+    <t>a2_auteur_3</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_3</t>
+  </si>
+  <si>
+    <t>2012-10-12</t>
+  </si>
+  <si>
+    <t>a2_producent_3</t>
+  </si>
+  <si>
+    <t>2004-06-20T16:23:19.296Z</t>
+  </si>
+  <si>
+    <t>a2_taal_3</t>
+  </si>
+  <si>
+    <t>a2_uitgever_3</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_3</t>
+  </si>
+  <si>
+    <t>a2_versie_3</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_4</t>
+  </si>
+  <si>
+    <t>a2_auteur_4</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_4</t>
+  </si>
+  <si>
+    <t>2028-05-14</t>
+  </si>
+  <si>
+    <t>a2_producent_4</t>
+  </si>
+  <si>
+    <t>2027-06-06T03:43:43.060Z</t>
+  </si>
+  <si>
+    <t>a2_taal_4</t>
+  </si>
+  <si>
+    <t>a2_uitgever_4</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_4</t>
+  </si>
+  <si>
+    <t>a2_versie_4</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_5</t>
+  </si>
+  <si>
+    <t>a2_auteur_5|a2_auteur_5b</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
+  </si>
+  <si>
+    <t>2008-08-30</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_2|a2/code/Licentie_1</t>
+  </si>
+  <si>
+    <t>a2_producent_5|a2_producent_5b</t>
+  </si>
+  <si>
+    <t>2022-11-10T10:58:41.888Z</t>
+  </si>
+  <si>
+    <t>a2_taal_5|a2_taal_5b</t>
+  </si>
+  <si>
+    <t>a2_uitgever_5|a2_uitgever_5b</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_5</t>
+  </si>
+  <si>
+    <t>a2_versie_5</t>
+  </si>
+  <si>
+    <t>bestaatUit</t>
+  </si>
+  <si>
+    <t>bron</t>
+  </si>
+  <si>
+    <t>competentie</t>
+  </si>
+  <si>
+    <t>doelgroep</t>
+  </si>
+  <si>
+    <t>gedefinieerdDoor</t>
+  </si>
+  <si>
+    <t>geldigheid</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>gerelateerdAan</t>
+  </si>
+  <si>
+    <t>heeftSpecialisatie</t>
+  </si>
+  <si>
+    <t>identificator</t>
+  </si>
+  <si>
+    <t>isBrederDan</t>
+  </si>
+  <si>
+    <t>isLidVan</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>onderwerp</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2_bron_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_1</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_1</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_1</t>
+  </si>
+  <si>
+    <t>a2_bron_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_2</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_2</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2_bron_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_3</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_3</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_3</t>
+  </si>
+  <si>
+    <t>a2_bron_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_4</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_4</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_4</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2_bron_5|a2_bron_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_3|a2/code/Competentie_5</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1|a2/code/DoelCollectie_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_5|a2_niveau_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
+  </si>
+  <si>
+    <t>a2_type_5|a2_type_5b</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_2</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_5</t>
+  </si>
+  <si>
+    <t>leeftijdstype</t>
+  </si>
+  <si>
+    <t>onderwijsniveau</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_1</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_1</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_2</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_3</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_4</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_5</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
+  </si>
+  <si>
+    <t>valuta</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_1</t>
+  </si>
+  <si>
+    <t>a2_valuta_1</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_2</t>
+  </si>
+  <si>
+    <t>a2_valuta_2</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_3</t>
+  </si>
+  <si>
+    <t>a2_valuta_3</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_4</t>
+  </si>
+  <si>
+    <t>a2_valuta_4</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_5</t>
+  </si>
+  <si>
+    <t>a2_valuta_5</t>
+  </si>
+  <si>
+    <t>toegekendDoor</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_1</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_2</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_4</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_5</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
+    <t>waarde</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_1</t>
+  </si>
+  <si>
+    <t>a2_eenheid_1</t>
+  </si>
+  <si>
+    <t>a2_waarde_1</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_2</t>
+  </si>
+  <si>
+    <t>a2_eenheid_2</t>
+  </si>
+  <si>
+    <t>a2_waarde_2</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_3</t>
+  </si>
+  <si>
+    <t>a2_eenheid_3</t>
+  </si>
+  <si>
+    <t>a2_waarde_3</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_4</t>
+  </si>
+  <si>
+    <t>a2_eenheid_4</t>
+  </si>
+  <si>
+    <t>a2_waarde_4</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_5</t>
+  </si>
+  <si>
+    <t>a2_eenheid_5</t>
+  </si>
+  <si>
+    <t>a2_waarde_5</t>
+  </si>
+  <si>
+    <t>draagtBijAanHetBehalenVan</t>
+  </si>
+  <si>
+    <t>heeftDeel</t>
+  </si>
+  <si>
+    <t>ingerichtDoor</t>
+  </si>
+  <si>
+    <t>isDeelVan</t>
+  </si>
+  <si>
+    <t>leermiddel</t>
+  </si>
+  <si>
+    <t>locatie</t>
+  </si>
+  <si>
+    <t>periode</t>
+  </si>
+  <si>
+    <t>specificatie</t>
+  </si>
+  <si>
+    <t>werklast</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2_periode_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_werklast_1</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4</t>
+  </si>
+  <si>
+    <t>a2_periode_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2_werklast_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2_periode_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2_periode_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1|a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4|a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4|a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Adresvoorstelling_1|a2/code/Adresvoorstelling_5</t>
+  </si>
+  <si>
+    <t>a2_periode_5|a2_periode_5b</t>
+  </si>
+  <si>
+    <t>a2_werklast_5</t>
+  </si>
+  <si>
+    <t>contacturen</t>
+  </si>
+  <si>
+    <t>generalisatieVan</t>
+  </si>
+  <si>
+    <t>instructietaal</t>
+  </si>
+  <si>
+    <t>schrijftVoor</t>
+  </si>
+  <si>
+    <t>specialisatieVan</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_3</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_5|a2/code/Openingsurenspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5|a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>benodigdMateriaal</t>
+  </si>
+  <si>
+    <t>dient</t>
+  </si>
+  <si>
+    <t>formaat</t>
+  </si>
+  <si>
+    <t>instructie</t>
+  </si>
+  <si>
+    <t>interactieType</t>
+  </si>
+  <si>
+    <t>kost</t>
+  </si>
+  <si>
+    <t>resultaat</t>
+  </si>
+  <si>
+    <t>sleutelwoord</t>
+  </si>
+  <si>
+    <t>toegankelijkheid</t>
+  </si>
+  <si>
+    <t>vereiste</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_3</t>
+  </si>
+  <si>
+    <t>a2_formaat_1</t>
+  </si>
+  <si>
+    <t>a2_instructie_1</t>
+  </si>
+  <si>
+    <t>a2_interactieType_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3</t>
+  </si>
+  <si>
+    <t>a2_resultaat_1</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_1</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_1</t>
+  </si>
+  <si>
+    <t>a2_vereiste_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_5</t>
+  </si>
+  <si>
+    <t>a2_formaat_2</t>
+  </si>
+  <si>
+    <t>a2_instructie_2</t>
+  </si>
+  <si>
+    <t>a2_interactieType_2</t>
+  </si>
+  <si>
+    <t>a2_resultaat_2</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_2</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_2</t>
+  </si>
+  <si>
+    <t>a2_vereiste_2</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_1</t>
+  </si>
+  <si>
+    <t>a2_formaat_3</t>
+  </si>
+  <si>
+    <t>a2_instructie_3</t>
+  </si>
+  <si>
+    <t>a2_interactieType_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_3</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_3</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_3</t>
+  </si>
+  <si>
+    <t>a2_vereiste_3</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2_formaat_4</t>
+  </si>
+  <si>
+    <t>a2_instructie_4</t>
+  </si>
+  <si>
+    <t>a2_interactieType_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_4</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_4</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_4</t>
+  </si>
+  <si>
+    <t>a2_vereiste_4</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2|a2/code/LeermiddelElement_4</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_5|a2/code/Competentie_1</t>
+  </si>
+  <si>
+    <t>a2_formaat_5|a2_formaat_5b</t>
+  </si>
+  <si>
+    <t>a2_instructie_5</t>
+  </si>
+  <si>
+    <t>a2_interactieType_5|a2_interactieType_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_4|a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2_resultaat_5|a2_resultaat_5b</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_5</t>
+  </si>
+  <si>
+    <t>a2_vereiste_5|a2_vereiste_5b</t>
+  </si>
+  <si>
+    <t>onderdeelVan</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_4</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_2</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_4</t>
   </si>
   <si>
     <t>a2/code/Licentie_5</t>
   </si>
   <si>
-    <t>a2_producent_1</t>
-  </si>
-  <si>
-    <t>2020-05-11T16:47:58.422Z</t>
-  </si>
-  <si>
-    <t>a2_taal_1</t>
-  </si>
-  <si>
-    <t>a2_uitgever_1</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_1</t>
-  </si>
-  <si>
-    <t>a2_versie_1</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_2</t>
-  </si>
-  <si>
-    <t>a2_auteur_2</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_2</t>
-  </si>
-  <si>
-    <t>2014-06-05</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_2</t>
-  </si>
-  <si>
-    <t>a2_producent_2</t>
-  </si>
-  <si>
-    <t>2023-08-08T03:09:58.027Z</t>
-  </si>
-  <si>
-    <t>a2_taal_2</t>
-  </si>
-  <si>
-    <t>a2_uitgever_2</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_2</t>
-  </si>
-  <si>
-    <t>a2_versie_2</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_3</t>
-  </si>
-  <si>
-    <t>a2_auteur_3</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_3</t>
-  </si>
-  <si>
-    <t>2022-02-10</t>
-  </si>
-  <si>
-    <t>a2_producent_3</t>
-  </si>
-  <si>
-    <t>2023-10-14T23:17:00.950Z</t>
-  </si>
-  <si>
-    <t>a2_taal_3</t>
-  </si>
-  <si>
-    <t>a2_uitgever_3</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_3</t>
-  </si>
-  <si>
-    <t>a2_versie_3</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_4</t>
-  </si>
-  <si>
-    <t>a2_auteur_4</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_4</t>
-  </si>
-  <si>
-    <t>2017-10-01</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_3</t>
-  </si>
-  <si>
-    <t>a2_producent_4</t>
-  </si>
-  <si>
-    <t>2006-10-19T23:59:43.710Z</t>
-  </si>
-  <si>
-    <t>a2_taal_4</t>
-  </si>
-  <si>
-    <t>a2_uitgever_4</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_4</t>
-  </si>
-  <si>
-    <t>a2_versie_4</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_5</t>
-  </si>
-  <si>
-    <t>a2_auteur_5|a2_auteur_5b</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
-  </si>
-  <si>
-    <t>2006-03-28</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_5|a2/code/Licentie_5</t>
-  </si>
-  <si>
-    <t>a2_producent_5|a2_producent_5b</t>
-  </si>
-  <si>
-    <t>2011-09-20T09:59:04.506Z</t>
-  </si>
-  <si>
-    <t>a2_taal_5|a2_taal_5b</t>
-  </si>
-  <si>
-    <t>a2_uitgever_5|a2_uitgever_5b</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_5</t>
-  </si>
-  <si>
-    <t>a2_versie_5</t>
-  </si>
-  <si>
-    <t>bestaatUit</t>
-  </si>
-  <si>
-    <t>bron</t>
-  </si>
-  <si>
-    <t>competentie</t>
-  </si>
-  <si>
-    <t>doelgroep</t>
-  </si>
-  <si>
-    <t>gedefinieerdDoor</t>
-  </si>
-  <si>
-    <t>geldigheid</t>
-  </si>
-  <si>
-    <t>gelijkaardig</t>
-  </si>
-  <si>
-    <t>gerelateerdAan</t>
-  </si>
-  <si>
-    <t>heeftSpecialisatie</t>
-  </si>
-  <si>
-    <t>identificator</t>
-  </si>
-  <si>
-    <t>isBrederDan</t>
-  </si>
-  <si>
-    <t>isLidVan</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>onderwerp</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_bron_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_1</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_1</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_1</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_1</t>
-  </si>
-  <si>
-    <t>a2_bron_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_2</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_2</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_2</t>
-  </si>
-  <si>
-    <t>a2_bron_3</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_3</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_3</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_3</t>
-  </si>
-  <si>
-    <t>a2_bron_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_4</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_4</t>
-  </si>
-  <si>
-    <t>a2_niveau_4</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2_bron_5|a2_bron_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_4|a2/code/Competentie_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_3|a2/code/DoelCollectie_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_5|a2_niveau_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
-  </si>
-  <si>
-    <t>a2_type_5|a2_type_5b</t>
-  </si>
-  <si>
-    <t>heeftLid</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_3</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_5</t>
-  </si>
-  <si>
-    <t>leeftijdstype</t>
-  </si>
-  <si>
-    <t>onderwijsniveau</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_1</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_1</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_2</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_3</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_4</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_5</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
-  </si>
-  <si>
-    <t>valuta</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_1</t>
-  </si>
-  <si>
-    <t>a2_valuta_1</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_2</t>
-  </si>
-  <si>
-    <t>a2_valuta_2</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_3</t>
-  </si>
-  <si>
-    <t>a2_valuta_3</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_4</t>
-  </si>
-  <si>
-    <t>a2_valuta_4</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_5</t>
-  </si>
-  <si>
-    <t>a2_valuta_5</t>
-  </si>
-  <si>
-    <t>toegekendDoor</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_1</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_2</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_3</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_3</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_5</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
-    <t>waarde</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_1</t>
-  </si>
-  <si>
-    <t>a2_eenheid_1</t>
-  </si>
-  <si>
-    <t>a2_waarde_1</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_2</t>
-  </si>
-  <si>
-    <t>a2_eenheid_2</t>
-  </si>
-  <si>
-    <t>a2_waarde_2</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_3</t>
-  </si>
-  <si>
-    <t>a2_eenheid_3</t>
-  </si>
-  <si>
-    <t>a2_waarde_3</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_4</t>
-  </si>
-  <si>
-    <t>a2_eenheid_4</t>
-  </si>
-  <si>
-    <t>a2_waarde_4</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_5</t>
-  </si>
-  <si>
-    <t>a2_eenheid_5</t>
-  </si>
-  <si>
-    <t>a2_waarde_5</t>
-  </si>
-  <si>
-    <t>draagtBijAanHetBehalenVan</t>
-  </si>
-  <si>
-    <t>heeftDeel</t>
-  </si>
-  <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
-    <t>isDeelVan</t>
-  </si>
-  <si>
-    <t>leermiddel</t>
-  </si>
-  <si>
-    <t>locatie</t>
-  </si>
-  <si>
-    <t>periode</t>
-  </si>
-  <si>
-    <t>specificatie</t>
-  </si>
-  <si>
-    <t>werklast</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2_periode_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_werklast_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2_periode_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_werklast_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2_periode_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2_werklast_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4</t>
-  </si>
-  <si>
-    <t>a2_periode_4</t>
-  </si>
-  <si>
-    <t>a2_werklast_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1|a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4|a2/code/Leeractiviteit_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1|a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Adresvoorstelling_4|a2/code/Adresvoorstelling_1</t>
-  </si>
-  <si>
-    <t>a2_periode_5|a2_periode_5b</t>
-  </si>
-  <si>
-    <t>a2_werklast_5</t>
-  </si>
-  <si>
-    <t>contacturen</t>
-  </si>
-  <si>
-    <t>generalisatieVan</t>
-  </si>
-  <si>
-    <t>instructietaal</t>
-  </si>
-  <si>
-    <t>schrijftVoor</t>
-  </si>
-  <si>
-    <t>specialisatieVan</t>
+    <t>dagVanDeWeek</t>
+  </si>
+  <si>
+    <t>geldigTot</t>
+  </si>
+  <si>
+    <t>geldigVan</t>
+  </si>
+  <si>
+    <t>gesloten</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_1</t>
+  </si>
+  <si>
+    <t>2008-03-21T18:40:11.736Z</t>
+  </si>
+  <si>
+    <t>2006-01-31T09:05:26.138Z</t>
+  </si>
+  <si>
+    <t>14:51:28</t>
+  </si>
+  <si>
+    <t>20:42:11</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_2</t>
+  </si>
+  <si>
+    <t>2023-09-23T02:43:59.717Z</t>
+  </si>
+  <si>
+    <t>2004-12-21T15:00:51.653Z</t>
+  </si>
+  <si>
+    <t>03:51:47</t>
+  </si>
+  <si>
+    <t>02:17:25</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_3</t>
+  </si>
+  <si>
+    <t>http://example.com/au/dagVanDeWeek_3</t>
+  </si>
+  <si>
+    <t>2004-07-14T00:05:29.229Z</t>
+  </si>
+  <si>
+    <t>2014-06-25T07:16:46.396Z</t>
+  </si>
+  <si>
+    <t>01:13:05</t>
+  </si>
+  <si>
+    <t>02:20:52</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_4</t>
   </si>
   <si>
-    <t>a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1</t>
+    <t>http://example.com/au/dagVanDeWeek_4</t>
+  </si>
+  <si>
+    <t>2008-05-24T04:45:56.408Z</t>
+  </si>
+  <si>
+    <t>2005-07-12T14:34:18.417Z</t>
+  </si>
+  <si>
+    <t>19:34:13</t>
+  </si>
+  <si>
+    <t>08:42:14</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_5</t>
   </si>
   <si>
-    <t>a2_instructietaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_4|a2/code/Openingsurenspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3|a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5|a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>benodigdMateriaal</t>
-  </si>
-  <si>
-    <t>dient</t>
-  </si>
-  <si>
-    <t>formaat</t>
-  </si>
-  <si>
-    <t>instructie</t>
-  </si>
-  <si>
-    <t>interactieType</t>
-  </si>
-  <si>
-    <t>kost</t>
-  </si>
-  <si>
-    <t>resultaat</t>
-  </si>
-  <si>
-    <t>sleutelwoord</t>
-  </si>
-  <si>
-    <t>toegankelijkheid</t>
-  </si>
-  <si>
-    <t>vereiste</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_3</t>
-  </si>
-  <si>
-    <t>a2_formaat_1</t>
-  </si>
-  <si>
-    <t>a2_instructie_1</t>
-  </si>
-  <si>
-    <t>a2_interactieType_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2_resultaat_1</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_1</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_1</t>
-  </si>
-  <si>
-    <t>a2_vereiste_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2_formaat_2</t>
-  </si>
-  <si>
-    <t>a2_instructie_2</t>
-  </si>
-  <si>
-    <t>a2_interactieType_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2_resultaat_2</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_2</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_2</t>
-  </si>
-  <si>
-    <t>a2_vereiste_2</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_3</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_5</t>
-  </si>
-  <si>
-    <t>a2_formaat_3</t>
-  </si>
-  <si>
-    <t>a2_instructie_3</t>
-  </si>
-  <si>
-    <t>a2_interactieType_3</t>
-  </si>
-  <si>
-    <t>a2_resultaat_3</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_3</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_3</t>
-  </si>
-  <si>
-    <t>a2_vereiste_3</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_4</t>
-  </si>
-  <si>
-    <t>a2_formaat_4</t>
-  </si>
-  <si>
-    <t>a2_instructie_4</t>
-  </si>
-  <si>
-    <t>a2_interactieType_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_4</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_4</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_4</t>
-  </si>
-  <si>
-    <t>a2_vereiste_4</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_1|a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_2|a2/code/Competentie_1</t>
-  </si>
-  <si>
-    <t>a2_formaat_5|a2_formaat_5b</t>
-  </si>
-  <si>
-    <t>a2_instructie_5</t>
-  </si>
-  <si>
-    <t>a2_interactieType_5|a2_interactieType_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_2|a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2_resultaat_5|a2_resultaat_5b</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_5</t>
-  </si>
-  <si>
-    <t>a2_vereiste_5|a2_vereiste_5b</t>
-  </si>
-  <si>
-    <t>onderdeelVan</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_3</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3|a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_4</t>
-  </si>
-  <si>
-    <t>dagVanDeWeek</t>
-  </si>
-  <si>
-    <t>geldigTot</t>
-  </si>
-  <si>
-    <t>geldigVan</t>
-  </si>
-  <si>
-    <t>gesloten</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_1</t>
-  </si>
-  <si>
-    <t>2018-06-04T14:27:36.396Z</t>
-  </si>
-  <si>
-    <t>2029-03-07T05:58:13.880Z</t>
-  </si>
-  <si>
-    <t>11:05:38</t>
-  </si>
-  <si>
-    <t>19:53:48</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_2</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_2</t>
-  </si>
-  <si>
-    <t>2025-11-20T23:52:58.245Z</t>
-  </si>
-  <si>
-    <t>2021-10-14T09:31:18.438Z</t>
-  </si>
-  <si>
-    <t>20:06:02</t>
-  </si>
-  <si>
-    <t>16:49:58</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_3</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_3</t>
-  </si>
-  <si>
-    <t>2024-12-30T15:20:36.799Z</t>
-  </si>
-  <si>
-    <t>2026-01-26T17:09:34.900Z</t>
-  </si>
-  <si>
-    <t>14:02:36</t>
-  </si>
-  <si>
-    <t>00:59:06</t>
-  </si>
-  <si>
-    <t>http://example.com/au/dagVanDeWeek_4</t>
-  </si>
-  <si>
-    <t>2006-02-08T00:12:23.233Z</t>
-  </si>
-  <si>
-    <t>2000-10-05T01:31:02.846Z</t>
-  </si>
-  <si>
-    <t>08:57:41</t>
-  </si>
-  <si>
-    <t>14:03:20</t>
-  </si>
-  <si>
     <t>http://example.com/au/dagVanDeWeek_5</t>
   </si>
   <si>
-    <t>2020-01-31T11:15:09.978Z</t>
-  </si>
-  <si>
-    <t>2029-07-22T14:49:56.409Z</t>
-  </si>
-  <si>
-    <t>00:32:45</t>
-  </si>
-  <si>
-    <t>11:16:02</t>
+    <t>2002-01-22T13:01:03.960Z</t>
+  </si>
+  <si>
+    <t>2018-08-15T14:26:45.421Z</t>
+  </si>
+  <si>
+    <t>04:42:39</t>
+  </si>
+  <si>
+    <t>18:03:04</t>
   </si>
   <si>
     <t>tot</t>
@@ -2260,209 +2257,209 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>92</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>236</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -2484,28 +2481,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>92</v>
@@ -2513,7 +2510,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>344</v>
@@ -2522,22 +2519,22 @@
         <v>191</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="G2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
@@ -2545,31 +2542,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
@@ -2577,31 +2574,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
@@ -2609,31 +2606,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>191</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2641,31 +2638,31 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>236</v>
@@ -2690,105 +2687,105 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G1" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>91</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>92</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>95</v>
@@ -2800,33 +2797,33 @@
         <v>201</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>202</v>
@@ -2835,155 +2832,155 @@
         <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="M4" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="Q4" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="L5" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>107</v>
@@ -2995,60 +2992,60 @@
         <v>223</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="J6" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="M6" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>111</v>
@@ -3060,19 +3057,19 @@
         <v>235</v>
       </c>
       <c r="Q6" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>236</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -3094,47 +3091,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3161,42 +3158,42 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>423</v>
+        <v>374</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3223,7 +3220,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>427</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>96</v>
@@ -3231,7 +3228,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>138</v>
+        <v>424</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>100</v>
@@ -3239,7 +3236,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>104</v>
@@ -3247,7 +3244,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
@@ -3255,7 +3252,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>426</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>236</v>
@@ -3280,119 +3277,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>344</v>
+        <v>448</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>352</v>
+        <v>454</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -3414,65 +3411,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -3491,63 +3488,63 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -3555,13 +3552,13 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -3569,13 +3566,13 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -3583,13 +3580,13 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -3597,13 +3594,13 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -3623,42 +3620,42 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -3927,60 +3924,60 @@
         <v>158</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4005,46 +4002,46 @@
         <v>90</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>92</v>
@@ -4052,43 +4049,43 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>199</v>
@@ -4105,19 +4102,19 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>202</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>203</v>
@@ -4129,28 +4126,28 @@
         <v>205</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>199</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>100</v>
@@ -4158,22 +4155,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>212</v>
@@ -4182,28 +4179,28 @@
         <v>213</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>214</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>104</v>
@@ -4211,43 +4208,43 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="M5" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>221</v>
@@ -4264,7 +4261,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>110</v>
@@ -4279,7 +4276,7 @@
         <v>226</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>227</v>
@@ -4291,13 +4288,13 @@
         <v>229</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>232</v>
@@ -4334,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>237</v>
@@ -4343,7 +4340,7 @@
         <v>91</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>92</v>
@@ -4351,13 +4348,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>95</v>
@@ -4371,19 +4368,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>100</v>
@@ -4397,13 +4394,13 @@
         <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>104</v>
@@ -4411,13 +4408,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>107</v>
@@ -4431,19 +4428,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>112</v>
@@ -4468,18 +4465,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>246</v>
@@ -4521,7 +4518,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>256</v>
@@ -4633,7 +4630,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>275</v>
@@ -4641,34 +4638,34 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -4690,65 +4687,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/example-data/dummydata-a2.xlsx
+++ b/example-data/dummydata-a2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="512">
   <si>
     <t>CODE</t>
   </si>
@@ -409,906 +409,921 @@
     <t>a2_auteursrechtHouder_1</t>
   </si>
   <si>
-    <t>2010-05-18</t>
+    <t>2030-08-01</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_1</t>
+  </si>
+  <si>
+    <t>a2_producent_1</t>
+  </si>
+  <si>
+    <t>2004-02-29T16:32:59.723Z</t>
+  </si>
+  <si>
+    <t>a2_taal_1</t>
+  </si>
+  <si>
+    <t>a2_uitgever_1</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_1</t>
+  </si>
+  <si>
+    <t>a2_versie_1</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_2</t>
+  </si>
+  <si>
+    <t>a2_auteur_2</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_2</t>
+  </si>
+  <si>
+    <t>2012-03-25</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_4</t>
+  </si>
+  <si>
+    <t>a2_producent_2</t>
+  </si>
+  <si>
+    <t>2012-06-21T21:00:55.627Z</t>
+  </si>
+  <si>
+    <t>a2_taal_2</t>
+  </si>
+  <si>
+    <t>a2_uitgever_2</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_2</t>
+  </si>
+  <si>
+    <t>a2_versie_2</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_3</t>
+  </si>
+  <si>
+    <t>a2_auteur_3</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_3</t>
+  </si>
+  <si>
+    <t>2010-01-27</t>
+  </si>
+  <si>
+    <t>a2_producent_3</t>
+  </si>
+  <si>
+    <t>2005-03-21T12:40:39.042Z</t>
+  </si>
+  <si>
+    <t>a2_taal_3</t>
+  </si>
+  <si>
+    <t>a2_uitgever_3</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_3</t>
+  </si>
+  <si>
+    <t>a2_versie_3</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_4</t>
+  </si>
+  <si>
+    <t>a2_auteur_4</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_4</t>
+  </si>
+  <si>
+    <t>2011-10-17</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_2</t>
+  </si>
+  <si>
+    <t>a2_producent_4</t>
+  </si>
+  <si>
+    <t>2024-02-15T05:35:59.056Z</t>
+  </si>
+  <si>
+    <t>a2_taal_4</t>
+  </si>
+  <si>
+    <t>a2_uitgever_4</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_4</t>
+  </si>
+  <si>
+    <t>a2_versie_4</t>
+  </si>
+  <si>
+    <t>a2/code/CreatiefWerk_5</t>
+  </si>
+  <si>
+    <t>a2_auteur_5|a2_auteur_5b</t>
+  </si>
+  <si>
+    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
+  </si>
+  <si>
+    <t>2028-03-28</t>
+  </si>
+  <si>
+    <t>a2/code/Licentie_5|a2/code/Licentie_5</t>
+  </si>
+  <si>
+    <t>a2_producent_5|a2_producent_5b</t>
+  </si>
+  <si>
+    <t>2029-09-06T12:55:36.223Z</t>
+  </si>
+  <si>
+    <t>a2_taal_5|a2_taal_5b</t>
+  </si>
+  <si>
+    <t>a2_uitgever_5|a2_uitgever_5b</t>
+  </si>
+  <si>
+    <t>a2_vereisteTijd_5</t>
+  </si>
+  <si>
+    <t>a2_versie_5</t>
+  </si>
+  <si>
+    <t>bestaatUit</t>
+  </si>
+  <si>
+    <t>bron</t>
+  </si>
+  <si>
+    <t>competentie</t>
+  </si>
+  <si>
+    <t>doelgroep</t>
+  </si>
+  <si>
+    <t>gedefinieerdDoor</t>
+  </si>
+  <si>
+    <t>geldigheid</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>gerelateerdAan</t>
+  </si>
+  <si>
+    <t>heeftSpecialisatie</t>
+  </si>
+  <si>
+    <t>identificator</t>
+  </si>
+  <si>
+    <t>isBrederDan</t>
+  </si>
+  <si>
+    <t>isLidVan</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>onderwerp</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2_bron_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_1</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_2</t>
+  </si>
+  <si>
+    <t>a2_niveau_1</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_1</t>
+  </si>
+  <si>
+    <t>a2_bron_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_2</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_3</t>
+  </si>
+  <si>
+    <t>a2_niveau_2</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2_bron_3</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_3</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_3</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_2</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_1</t>
+  </si>
+  <si>
+    <t>a2_niveau_3</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_3</t>
+  </si>
+  <si>
+    <t>a2_bron_4</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_4</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2_niveau_4</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2_bron_5|a2_bron_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_1|a2/code/Competentie_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
+  </si>
+  <si>
+    <t>a2_geldigheid_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_4|a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_3|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_4</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3|a2/code/DoelCollectie_4</t>
+  </si>
+  <si>
+    <t>a2_niveau_5|a2_niveau_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
+  </si>
+  <si>
+    <t>a2_type_5|a2_type_5b</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_3</t>
+  </si>
+  <si>
+    <t>a2/code/DoelCollectie_5</t>
+  </si>
+  <si>
+    <t>a2_gedefinieerdDoor_5</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2|a2/code/Doel_5</t>
+  </si>
+  <si>
+    <t>a2_niveau_5</t>
+  </si>
+  <si>
+    <t>leeftijdstype</t>
+  </si>
+  <si>
+    <t>onderwijsniveau</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_1</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_1</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_1</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_2</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_2</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_3</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_3</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_3</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_4</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_4</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doelgroep_5</t>
+  </si>
+  <si>
+    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
+  </si>
+  <si>
+    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
+  </si>
+  <si>
+    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
+  </si>
+  <si>
+    <t>valuta</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_1</t>
+  </si>
+  <si>
+    <t>a2_valuta_1</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_2</t>
+  </si>
+  <si>
+    <t>a2_valuta_2</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_3</t>
+  </si>
+  <si>
+    <t>a2_valuta_3</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_4</t>
+  </si>
+  <si>
+    <t>a2_valuta_4</t>
+  </si>
+  <si>
+    <t>a2/code/Geldbedrag_5</t>
+  </si>
+  <si>
+    <t>a2_valuta_5</t>
+  </si>
+  <si>
+    <t>toegekendDoor</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_1</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_1</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_2</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_3</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_4</t>
+  </si>
+  <si>
+    <t>a2/code/Identificator_5</t>
+  </si>
+  <si>
+    <t>a2_toegekendDoor_5</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
+    <t>waarde</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_1</t>
+  </si>
+  <si>
+    <t>a2_eenheid_1</t>
+  </si>
+  <si>
+    <t>a2_waarde_1</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_2</t>
+  </si>
+  <si>
+    <t>a2_eenheid_2</t>
+  </si>
+  <si>
+    <t>a2_waarde_2</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_3</t>
+  </si>
+  <si>
+    <t>a2_eenheid_3</t>
+  </si>
+  <si>
+    <t>a2_waarde_3</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_4</t>
+  </si>
+  <si>
+    <t>a2_eenheid_4</t>
+  </si>
+  <si>
+    <t>a2_waarde_4</t>
+  </si>
+  <si>
+    <t>a2/code/KwantitatieveWaarde_5</t>
+  </si>
+  <si>
+    <t>a2_eenheid_5</t>
+  </si>
+  <si>
+    <t>a2_waarde_5</t>
+  </si>
+  <si>
+    <t>draagtBijAanHetBehalenVan</t>
+  </si>
+  <si>
+    <t>heeftDeel</t>
+  </si>
+  <si>
+    <t>ingerichtDoor</t>
+  </si>
+  <si>
+    <t>isDeelVan</t>
+  </si>
+  <si>
+    <t>leermiddel</t>
+  </si>
+  <si>
+    <t>locatie</t>
+  </si>
+  <si>
+    <t>periode</t>
+  </si>
+  <si>
+    <t>specificatie</t>
+  </si>
+  <si>
+    <t>werklast</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4</t>
+  </si>
+  <si>
+    <t>a2_periode_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_werklast_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2_periode_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_2</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_3</t>
+  </si>
+  <si>
+    <t>a2_periode_3</t>
+  </si>
+  <si>
+    <t>a2_werklast_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_1</t>
+  </si>
+  <si>
+    <t>a2_periode_4</t>
+  </si>
+  <si>
+    <t>a2_werklast_4</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_1|a2/code/Doel_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_2|a2/code/Leeractiviteit_3</t>
+  </si>
+  <si>
+    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteit_5|a2/code/Leeractiviteit_4</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_5|a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Adresvoorstelling_5|a2/code/Adresvoorstelling_5</t>
+  </si>
+  <si>
+    <t>a2_periode_5|a2_periode_5b</t>
+  </si>
+  <si>
+    <t>a2_werklast_5</t>
+  </si>
+  <si>
+    <t>contacturen</t>
+  </si>
+  <si>
+    <t>generalisatieVan</t>
+  </si>
+  <si>
+    <t>instructietaal</t>
+  </si>
+  <si>
+    <t>schrijftVoor</t>
+  </si>
+  <si>
+    <t>specialisatieVan</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_3</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_4</t>
+  </si>
+  <si>
+    <t>a2/code/Openingsurenspecificatie_1|a2/code/Openingsurenspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_5|a2/code/Doel_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_3</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_2</t>
+  </si>
+  <si>
+    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_4|a2/code/Leermiddel_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_1</t>
+  </si>
+  <si>
+    <t>benodigdMateriaal</t>
+  </si>
+  <si>
+    <t>dient</t>
+  </si>
+  <si>
+    <t>formaat</t>
+  </si>
+  <si>
+    <t>instructie</t>
+  </si>
+  <si>
+    <t>interactieType</t>
+  </si>
+  <si>
+    <t>kost</t>
+  </si>
+  <si>
+    <t>resultaat</t>
+  </si>
+  <si>
+    <t>sleutelwoord</t>
+  </si>
+  <si>
+    <t>toegankelijkheid</t>
+  </si>
+  <si>
+    <t>vereiste</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_2</t>
+  </si>
+  <si>
+    <t>a2_formaat_1</t>
+  </si>
+  <si>
+    <t>a2_instructie_1</t>
+  </si>
+  <si>
+    <t>a2_interactieType_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_1</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_1</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_1</t>
+  </si>
+  <si>
+    <t>a2_vereiste_1</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_4</t>
+  </si>
+  <si>
+    <t>a2_formaat_2</t>
+  </si>
+  <si>
+    <t>a2_instructie_2</t>
+  </si>
+  <si>
+    <t>a2_interactieType_2</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_2</t>
+  </si>
+  <si>
+    <t>a2_resultaat_2</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_2</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_2</t>
+  </si>
+  <si>
+    <t>a2_vereiste_2</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_3</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_3</t>
+  </si>
+  <si>
+    <t>a2_formaat_3</t>
+  </si>
+  <si>
+    <t>a2_instructie_3</t>
+  </si>
+  <si>
+    <t>a2_interactieType_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_1</t>
+  </si>
+  <si>
+    <t>a2_resultaat_3</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_3</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_3</t>
+  </si>
+  <si>
+    <t>a2_vereiste_3</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_4</t>
+  </si>
+  <si>
+    <t>a2_formaat_4</t>
+  </si>
+  <si>
+    <t>a2_instructie_4</t>
+  </si>
+  <si>
+    <t>a2_interactieType_4</t>
+  </si>
+  <si>
+    <t>a2_resultaat_4</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_4</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_4</t>
+  </si>
+  <si>
+    <t>a2_vereiste_4</t>
+  </si>
+  <si>
+    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_5|a2/code/LeermiddelElement_3</t>
+  </si>
+  <si>
+    <t>a2/code/Competentie_1|a2/code/Competentie_1</t>
+  </si>
+  <si>
+    <t>a2/code/Doel_2|a2/code/Doel_1</t>
+  </si>
+  <si>
+    <t>a2_formaat_5|a2_formaat_5b</t>
+  </si>
+  <si>
+    <t>a2_instructie_5</t>
+  </si>
+  <si>
+    <t>a2_interactieType_5|a2_interactieType_5b</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3|a2/code/LeermiddelVerzameling_3</t>
+  </si>
+  <si>
+    <t>a2_resultaat_5|a2_resultaat_5b</t>
+  </si>
+  <si>
+    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
+  </si>
+  <si>
+    <t>a2_toegankelijkheid_5</t>
+  </si>
+  <si>
+    <t>a2_vereiste_5|a2_vereiste_5b</t>
+  </si>
+  <si>
+    <t>onderdeelVan</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_1</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelElement_5</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_3</t>
+  </si>
+  <si>
+    <t>a2/code/LeermiddelVerzameling_5</t>
+  </si>
+  <si>
+    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
   </si>
   <si>
     <t>a2/code/Licentie_3</t>
   </si>
   <si>
-    <t>a2_producent_1</t>
-  </si>
-  <si>
-    <t>2000-05-07T09:41:38.431Z</t>
-  </si>
-  <si>
-    <t>a2_taal_1</t>
-  </si>
-  <si>
-    <t>a2_uitgever_1</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_1</t>
-  </si>
-  <si>
-    <t>a2_versie_1</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_2</t>
-  </si>
-  <si>
-    <t>a2_auteur_2</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_2</t>
-  </si>
-  <si>
-    <t>2001-10-11</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2_producent_2</t>
-  </si>
-  <si>
-    <t>2013-06-07T07:02:06.954Z</t>
-  </si>
-  <si>
-    <t>a2_taal_2</t>
-  </si>
-  <si>
-    <t>a2_uitgever_2</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_2</t>
-  </si>
-  <si>
-    <t>a2_versie_2</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_3</t>
-  </si>
-  <si>
-    <t>a2_auteur_3</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_3</t>
-  </si>
-  <si>
-    <t>2012-10-12</t>
-  </si>
-  <si>
-    <t>a2_producent_3</t>
-  </si>
-  <si>
-    <t>2004-06-20T16:23:19.296Z</t>
-  </si>
-  <si>
-    <t>a2_taal_3</t>
-  </si>
-  <si>
-    <t>a2_uitgever_3</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_3</t>
-  </si>
-  <si>
-    <t>a2_versie_3</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_4</t>
-  </si>
-  <si>
-    <t>a2_auteur_4</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_4</t>
-  </si>
-  <si>
-    <t>2028-05-14</t>
-  </si>
-  <si>
-    <t>a2_producent_4</t>
-  </si>
-  <si>
-    <t>2027-06-06T03:43:43.060Z</t>
-  </si>
-  <si>
-    <t>a2_taal_4</t>
-  </si>
-  <si>
-    <t>a2_uitgever_4</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_4</t>
-  </si>
-  <si>
-    <t>a2_versie_4</t>
-  </si>
-  <si>
-    <t>a2/code/CreatiefWerk_5</t>
-  </si>
-  <si>
-    <t>a2_auteur_5|a2_auteur_5b</t>
-  </si>
-  <si>
-    <t>a2_auteursrechtHouder_5|a2_auteursrechtHouder_5b</t>
-  </si>
-  <si>
-    <t>2008-08-30</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_2|a2/code/Licentie_1</t>
-  </si>
-  <si>
-    <t>a2_producent_5|a2_producent_5b</t>
-  </si>
-  <si>
-    <t>2022-11-10T10:58:41.888Z</t>
-  </si>
-  <si>
-    <t>a2_taal_5|a2_taal_5b</t>
-  </si>
-  <si>
-    <t>a2_uitgever_5|a2_uitgever_5b</t>
-  </si>
-  <si>
-    <t>a2_vereisteTijd_5</t>
-  </si>
-  <si>
-    <t>a2_versie_5</t>
-  </si>
-  <si>
-    <t>bestaatUit</t>
-  </si>
-  <si>
-    <t>bron</t>
-  </si>
-  <si>
-    <t>competentie</t>
-  </si>
-  <si>
-    <t>doelgroep</t>
-  </si>
-  <si>
-    <t>gedefinieerdDoor</t>
-  </si>
-  <si>
-    <t>geldigheid</t>
-  </si>
-  <si>
-    <t>gelijkaardig</t>
-  </si>
-  <si>
-    <t>gerelateerdAan</t>
-  </si>
-  <si>
-    <t>heeftSpecialisatie</t>
-  </si>
-  <si>
-    <t>identificator</t>
-  </si>
-  <si>
-    <t>isBrederDan</t>
-  </si>
-  <si>
-    <t>isLidVan</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>onderwerp</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2_bron_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_1</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_1</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_1</t>
-  </si>
-  <si>
-    <t>a2_bron_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_2</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_2</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_2</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_bron_3</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_3</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_2</t>
-  </si>
-  <si>
-    <t>a2_niveau_3</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_3</t>
-  </si>
-  <si>
-    <t>a2_bron_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_4</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_4</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_4</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_4</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_2|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2_bron_5|a2_bron_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_3|a2/code/Competentie_5</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5|a2_gedefinieerdDoor_5b</t>
-  </si>
-  <si>
-    <t>a2_geldigheid_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_3</t>
-  </si>
-  <si>
-    <t>a2/code/Identificator_1</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_2</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_1|a2/code/DoelCollectie_5</t>
-  </si>
-  <si>
-    <t>a2_niveau_5|a2_niveau_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwerp_5|a2_onderwerp_5b</t>
-  </si>
-  <si>
-    <t>a2_type_5|a2_type_5b</t>
-  </si>
-  <si>
-    <t>heeftLid</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_2</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_3</t>
-  </si>
-  <si>
-    <t>a2/code/DoelCollectie_4</t>
-  </si>
-  <si>
-    <t>a2_gedefinieerdDoor_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_5|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2_niveau_5</t>
-  </si>
-  <si>
-    <t>leeftijdstype</t>
-  </si>
-  <si>
-    <t>onderwijsniveau</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_1</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_1</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_1</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_2</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_2</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_2</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_3</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_3</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_3</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_4</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_4</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doelgroep_5</t>
-  </si>
-  <si>
-    <t>a2_doelgroep_5|a2_doelgroep_5b</t>
-  </si>
-  <si>
-    <t>a2_leeftijdstype_5|a2_leeftijdstype_5b</t>
-  </si>
-  <si>
-    <t>a2_onderwijsniveau_5|a2_onderwijsniveau_5b</t>
-  </si>
-  <si>
-    <t>valuta</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_1</t>
-  </si>
-  <si>
-    <t>a2_valuta_1</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_2</t>
-  </si>
-  <si>
-    <t>a2_valuta_2</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_3</t>
-  </si>
-  <si>
-    <t>a2_valuta_3</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_4</t>
-  </si>
-  <si>
-    <t>a2_valuta_4</t>
-  </si>
-  <si>
-    <t>a2/code/Geldbedrag_5</t>
-  </si>
-  <si>
-    <t>a2_valuta_5</t>
-  </si>
-  <si>
-    <t>toegekendDoor</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_1</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_2</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_3</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_4</t>
-  </si>
-  <si>
-    <t>a2_toegekendDoor_5</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
-    <t>waarde</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_1</t>
-  </si>
-  <si>
-    <t>a2_eenheid_1</t>
-  </si>
-  <si>
-    <t>a2_waarde_1</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_2</t>
-  </si>
-  <si>
-    <t>a2_eenheid_2</t>
-  </si>
-  <si>
-    <t>a2_waarde_2</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_3</t>
-  </si>
-  <si>
-    <t>a2_eenheid_3</t>
-  </si>
-  <si>
-    <t>a2_waarde_3</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_4</t>
-  </si>
-  <si>
-    <t>a2_eenheid_4</t>
-  </si>
-  <si>
-    <t>a2_waarde_4</t>
-  </si>
-  <si>
-    <t>a2/code/KwantitatieveWaarde_5</t>
-  </si>
-  <si>
-    <t>a2_eenheid_5</t>
-  </si>
-  <si>
-    <t>a2_waarde_5</t>
-  </si>
-  <si>
-    <t>draagtBijAanHetBehalenVan</t>
-  </si>
-  <si>
-    <t>heeftDeel</t>
-  </si>
-  <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
-    <t>isDeelVan</t>
-  </si>
-  <si>
-    <t>leermiddel</t>
-  </si>
-  <si>
-    <t>locatie</t>
-  </si>
-  <si>
-    <t>periode</t>
-  </si>
-  <si>
-    <t>specificatie</t>
-  </si>
-  <si>
-    <t>werklast</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_2</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5</t>
-  </si>
-  <si>
-    <t>a2_periode_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2_werklast_1</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4</t>
-  </si>
-  <si>
-    <t>a2_periode_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2_werklast_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_3</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2_periode_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2_periode_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>a2_werklast_4</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_4|a2/code/Doel_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_1|a2/code/Leeractiviteit_3</t>
-  </si>
-  <si>
-    <t>a2_ingerichtDoor_5|a2_ingerichtDoor_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteit_4|a2/code/Leeractiviteit_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_4|a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Adresvoorstelling_1|a2/code/Adresvoorstelling_5</t>
-  </si>
-  <si>
-    <t>a2_periode_5|a2_periode_5b</t>
-  </si>
-  <si>
-    <t>a2_werklast_5</t>
-  </si>
-  <si>
-    <t>contacturen</t>
-  </si>
-  <si>
-    <t>generalisatieVan</t>
-  </si>
-  <si>
-    <t>instructietaal</t>
-  </si>
-  <si>
-    <t>schrijftVoor</t>
-  </si>
-  <si>
-    <t>specialisatieVan</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_3</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_3</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_2</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_5|a2/code/Openingsurenspecificatie_5</t>
-  </si>
-  <si>
-    <t>a2/code/Doel_1|a2/code/Doel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_5|a2/code/Leeractiviteitspecificatie_4</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_2|a2/code/Leeractiviteitspecificatie_1</t>
-  </si>
-  <si>
-    <t>a2_instructietaal_5|a2_instructietaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_5|a2/code/Leermiddel_1</t>
-  </si>
-  <si>
-    <t>a2/code/Leeractiviteitspecificatie_4|a2/code/Leeractiviteitspecificatie_3</t>
-  </si>
-  <si>
-    <t>benodigdMateriaal</t>
-  </si>
-  <si>
-    <t>dient</t>
-  </si>
-  <si>
-    <t>formaat</t>
-  </si>
-  <si>
-    <t>instructie</t>
-  </si>
-  <si>
-    <t>interactieType</t>
-  </si>
-  <si>
-    <t>kost</t>
-  </si>
-  <si>
-    <t>resultaat</t>
-  </si>
-  <si>
-    <t>sleutelwoord</t>
-  </si>
-  <si>
-    <t>toegankelijkheid</t>
-  </si>
-  <si>
-    <t>vereiste</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_3</t>
-  </si>
-  <si>
-    <t>a2_formaat_1</t>
-  </si>
-  <si>
-    <t>a2_instructie_1</t>
-  </si>
-  <si>
-    <t>a2_interactieType_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_3</t>
-  </si>
-  <si>
-    <t>a2_resultaat_1</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_1</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_1</t>
-  </si>
-  <si>
-    <t>a2_vereiste_1</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_5</t>
-  </si>
-  <si>
-    <t>a2_formaat_2</t>
-  </si>
-  <si>
-    <t>a2_instructie_2</t>
-  </si>
-  <si>
-    <t>a2_interactieType_2</t>
-  </si>
-  <si>
-    <t>a2_resultaat_2</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_2</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_2</t>
-  </si>
-  <si>
-    <t>a2_vereiste_2</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_3</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_1</t>
-  </si>
-  <si>
-    <t>a2_formaat_3</t>
-  </si>
-  <si>
-    <t>a2_instructie_3</t>
-  </si>
-  <si>
-    <t>a2_interactieType_3</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_3</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_3</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_3</t>
-  </si>
-  <si>
-    <t>a2_vereiste_3</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2</t>
-  </si>
-  <si>
-    <t>a2_formaat_4</t>
-  </si>
-  <si>
-    <t>a2_instructie_4</t>
-  </si>
-  <si>
-    <t>a2_interactieType_4</t>
-  </si>
-  <si>
-    <t>a2_resultaat_4</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_4</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_4</t>
-  </si>
-  <si>
-    <t>a2_vereiste_4</t>
-  </si>
-  <si>
-    <t>a2_benodigdMateriaal_5|a2_benodigdMateriaal_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_2|a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2/code/Competentie_5|a2/code/Competentie_1</t>
-  </si>
-  <si>
-    <t>a2_formaat_5|a2_formaat_5b</t>
-  </si>
-  <si>
-    <t>a2_instructie_5</t>
-  </si>
-  <si>
-    <t>a2_interactieType_5|a2_interactieType_5b</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_4|a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2_resultaat_5|a2_resultaat_5b</t>
-  </si>
-  <si>
-    <t>a2_sleutelwoord_5|a2_sleutelwoord_5b</t>
-  </si>
-  <si>
-    <t>a2_toegankelijkheid_5</t>
-  </si>
-  <si>
-    <t>a2_vereiste_5|a2_vereiste_5b</t>
-  </si>
-  <si>
-    <t>onderdeelVan</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelElement_4</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_1</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_2</t>
-  </si>
-  <si>
-    <t>a2/code/LeermiddelVerzameling_5</t>
-  </si>
-  <si>
-    <t>a2/code/Leermiddel_2|a2/code/Leermiddel_2</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_2</t>
-  </si>
-  <si>
-    <t>a2/code/Licentie_4</t>
-  </si>
-  <si>
     <t>a2/code/Licentie_5</t>
   </si>
   <si>
@@ -1330,49 +1345,46 @@
     <t>http://example.com/au/dagVanDeWeek_1</t>
   </si>
   <si>
-    <t>2008-03-21T18:40:11.736Z</t>
-  </si>
-  <si>
-    <t>2006-01-31T09:05:26.138Z</t>
-  </si>
-  <si>
-    <t>14:51:28</t>
-  </si>
-  <si>
-    <t>20:42:11</t>
+    <t>2014-05-17T03:21:37.107Z</t>
+  </si>
+  <si>
+    <t>2004-05-05T15:23:40.449Z</t>
+  </si>
+  <si>
+    <t>16:25:01</t>
+  </si>
+  <si>
+    <t>23:26:41</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_2</t>
   </si>
   <si>
-    <t>2023-09-23T02:43:59.717Z</t>
-  </si>
-  <si>
-    <t>2004-12-21T15:00:51.653Z</t>
-  </si>
-  <si>
-    <t>03:51:47</t>
-  </si>
-  <si>
-    <t>02:17:25</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_3</t>
+    <t>2025-01-19T10:21:17.213Z</t>
+  </si>
+  <si>
+    <t>2006-06-14T02:43:17.508Z</t>
+  </si>
+  <si>
+    <t>13:14:47</t>
+  </si>
+  <si>
+    <t>01:54:14</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_3</t>
   </si>
   <si>
-    <t>2004-07-14T00:05:29.229Z</t>
-  </si>
-  <si>
-    <t>2014-06-25T07:16:46.396Z</t>
-  </si>
-  <si>
-    <t>01:13:05</t>
-  </si>
-  <si>
-    <t>02:20:52</t>
+    <t>2023-03-26T08:49:14.715Z</t>
+  </si>
+  <si>
+    <t>2005-04-07T14:46:38.824Z</t>
+  </si>
+  <si>
+    <t>18:19:33</t>
+  </si>
+  <si>
+    <t>08:59:24</t>
   </si>
   <si>
     <t>a2/code/Openingsurenspecificatie_4</t>
@@ -1381,34 +1393,31 @@
     <t>http://example.com/au/dagVanDeWeek_4</t>
   </si>
   <si>
-    <t>2008-05-24T04:45:56.408Z</t>
-  </si>
-  <si>
-    <t>2005-07-12T14:34:18.417Z</t>
-  </si>
-  <si>
-    <t>19:34:13</t>
-  </si>
-  <si>
-    <t>08:42:14</t>
-  </si>
-  <si>
-    <t>a2/code/Openingsurenspecificatie_5</t>
+    <t>2016-04-29T01:48:27.164Z</t>
+  </si>
+  <si>
+    <t>2004-06-05T10:17:38.123Z</t>
+  </si>
+  <si>
+    <t>13:22:18</t>
+  </si>
+  <si>
+    <t>17:33:25</t>
   </si>
   <si>
     <t>http://example.com/au/dagVanDeWeek_5</t>
   </si>
   <si>
-    <t>2002-01-22T13:01:03.960Z</t>
-  </si>
-  <si>
-    <t>2018-08-15T14:26:45.421Z</t>
-  </si>
-  <si>
-    <t>04:42:39</t>
-  </si>
-  <si>
-    <t>18:03:04</t>
+    <t>2023-06-11T02:21:40.212Z</t>
+  </si>
+  <si>
+    <t>2030-01-23T23:44:38.423Z</t>
+  </si>
+  <si>
+    <t>21:06:26</t>
+  </si>
+  <si>
+    <t>08:11:40</t>
   </si>
   <si>
     <t>tot</t>
@@ -2257,168 +2266,168 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>92</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2429,7 +2438,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>330</v>
@@ -2453,10 +2462,10 @@
         <v>336</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>337</v>
@@ -2484,19 +2493,19 @@
         <v>338</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>340</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>341</v>
@@ -2516,22 +2525,22 @@
         <v>344</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>345</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>343</v>
@@ -2542,31 +2551,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>100</v>
@@ -2574,31 +2583,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>104</v>
@@ -2606,31 +2615,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>108</v>
@@ -2638,34 +2647,34 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2687,105 +2696,105 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>340</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>91</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>92</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>345</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>95</v>
@@ -2797,190 +2806,190 @@
         <v>201</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>202</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>100</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>104</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>191</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>107</v>
@@ -2992,84 +3001,84 @@
         <v>223</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3091,47 +3100,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>370</v>
+        <v>425</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3153,47 +3162,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>314</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -3220,7 +3229,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>96</v>
@@ -3228,7 +3237,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>424</v>
+        <v>159</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>100</v>
@@ -3236,7 +3245,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>430</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>104</v>
@@ -3244,7 +3253,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>425</v>
+        <v>138</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
@@ -3252,10 +3261,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3277,119 +3286,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>442</v>
+        <v>350</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>454</v>
+        <v>344</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3411,65 +3420,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -3488,63 +3497,63 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -3552,13 +3561,13 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -3566,13 +3575,13 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -3580,13 +3589,13 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -3594,13 +3603,13 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -3620,42 +3629,42 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -3924,60 +3933,60 @@
         <v>158</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4002,46 +4011,46 @@
         <v>90</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>92</v>
@@ -4049,43 +4058,43 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>199</v>
@@ -4102,13 +4111,13 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>202</v>
@@ -4126,28 +4135,28 @@
         <v>205</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>199</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>100</v>
@@ -4155,22 +4164,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>212</v>
@@ -4179,28 +4188,28 @@
         <v>213</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>214</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>104</v>
@@ -4208,43 +4217,43 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>221</v>
@@ -4261,7 +4270,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>110</v>
@@ -4276,40 +4285,40 @@
         <v>226</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4331,16 +4340,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>92</v>
@@ -4348,13 +4357,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>95</v>
@@ -4368,19 +4377,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>100</v>
@@ -4394,13 +4403,13 @@
         <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>104</v>
@@ -4408,13 +4417,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>107</v>
@@ -4428,7 +4437,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>241</v>
@@ -4465,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>244</v>
@@ -4476,7 +4485,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>246</v>
@@ -4490,7 +4499,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>249</v>
@@ -4518,7 +4527,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>256</v>
@@ -4630,10 +4639,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4641,31 +4650,31 @@
         <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -4687,65 +4696,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
